--- a/cleaning_pipeline_R/neotree_scripts/mwi-scripts/Neotree Admission KCH - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/mwi-scripts/Neotree Admission KCH - metadata.xlsx
@@ -577,7 +577,7 @@
         <v>$BabyCryTriage = false</v>
       </c>
       <c r="N3" t="str">
-        <v>[{"value":"NotBr","valueLabel":"NOT BREATHING! ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gasp","valueLabel":"GASPING or irregular breathing ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HRLow","valueLabel":"Normal breathing but HR &lt; 100 ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Floppy","valueLabel":"VERY FLOPPY (normal breathing &amp; HR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Stable","valueLabel":"Stable ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"NotBr","valueLabel":"NOT BREATHING!","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Gasp","valueLabel":"GASPING or irregular breathing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HRLow","valueLabel":"Normal breathing but HR &lt; 100","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Floppy","valueLabel":"VERY FLOPPY (normal breathing &amp; HR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Stable","valueLabel":"Stable","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O3" t="str">
         <v>$BabyCryTriage = false</v>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="V4" t="str">
-        <v>{"actionText":"RESUSCITATION","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Resuscitate the baby:","title2":"How to use Bag-Valve-Mask:","title3":"When stable continue with NeoTree","title4":"","text1":"","text2":"","text3":"If no HR for &gt; 10 minutes or remains &lt; 60/min for 20 mins STOP resuscitating but CONTINUE with NeoTree","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/1be556fa-70c2-48bd-ab8e-1c503400cb93?height=1076&amp;width=588","fileId":"1be556fa-70c2-48bd-ab8e-1c503400cb93","filename":"HBB action plan.jpg","size":"84101"},"image2":{"data":"https://webeditor.neotree.org/files/e0bc71a2-edf0-4759-a58c-b8753e15b6c8?height=312&amp;width=320","fileId":"e0bc71a2-edf0-4759-a58c-b8753e15b6c8","filename":"BVMblue.png","size":"89015"},"image3":{"data":"https://webeditor.neotree.org/files/a836bf2f-e179-440b-bb0c-87b8028266de?height=431&amp;width=447","fileId":"a836bf2f-e179-440b-bb0c-87b8028266de","filename":"Screen Shot 2016-04-22 at 10.26.33.png","size":"108712"}}}</v>
+        <v>{"actionText":"RESUSCITATION","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Resuscitate the baby:","title2":"How to use Bag-Valve-Mask:","title3":"When stable continue with NeoTree","title4":"","text1":"","text2":"","text3":"If no HR for &gt; 10 minutes or remains &lt; 60/min for 20 mins STOP resuscitating but CONTINUE with NeoTree","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/1be556fa-70c2-48bd-ab8e-1c503400cb93?height=1076&amp;width=588","fileId":"1be556fa-70c2-48bd-ab8e-1c503400cb93","filename":"HBB action plan.jpg","size":"84101"},"image2":{"data":"https://webeditor.neotree.org/files/e0bc71a2-edf0-4759-a58c-b8753e15b6c8?height=312&amp;type=png&amp;width=320","fileId":"e0bc71a2-edf0-4759-a58c-b8753e15b6c8","filename":"BVMblue.png","size":"89015"},"image3":{"data":"https://webeditor.neotree.org/files/a836bf2f-e179-440b-bb0c-87b8028266de?height=431&amp;width=447","fileId":"a836bf2f-e179-440b-bb0c-87b8028266de","filename":"Screen Shot 2016-04-22 at 10.26.33.png","size":"108712"}}}</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
         <v>DangerSigns</v>
       </c>
       <c r="G6" t="str">
-        <v xml:space="preserve">Danger signs </v>
+        <v>Danger signs</v>
       </c>
       <c r="H6" t="str">
         <v>multi_select_option</v>
@@ -819,7 +819,7 @@
         <v xml:space="preserve">EMERGENCY MANAGEMENT </v>
       </c>
       <c r="D7" t="str">
-        <v xml:space="preserve">Convulsions </v>
+        <v>Severe Resp distress1</v>
       </c>
       <c r="E7" t="str">
         <v>management</v>
@@ -852,7 +852,7 @@
         <v/>
       </c>
       <c r="O7" t="str">
-        <v xml:space="preserve">$DangerSigns = 'Convulsions' </v>
+        <v xml:space="preserve">$DangerSigns = 'Grun' </v>
       </c>
       <c r="P7" t="str">
         <v/>
@@ -873,7 +873,7 @@
         <v/>
       </c>
       <c r="V7" t="str">
-        <v>{"actionText":"CONVULSIONS ","contentText":"Refer to management of convulsions flow chart on wall","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"1. Airway management &amp; oxygen ","title2":"2. Check blood glucose ","title3":"3. Give anticonvulsants","title4":"","text1":"- Neutral position\n- Check for secretions, suction if needed \n- Put on oxygen","text2":"- If &lt; 45 mg/dl or &lt; 2.5 mmol/L give IV 10% glucose at 2ml/kg\n- If blood glucose monitoring not available give IV 10% glucose at 2ml/kg\n- Do full infection screen\n- If possible take blood for Ca, Mg, U and E’s, FBC","text3":"- Give phenobarbitone 20mg/kg IM \n- Repeat loading dose if necessary\n- If seizures ongoing give Paraldehyde Dose: 0.2 ml/kg IM, 0.4 ml/kg PR \n- If seizures still ongoing - give maintenance phenobarbitone 5mg/kg PO/IM\n\nWhen seizures have stopped and baby stable click the blue arrow to continue ","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
+        <v>{"actionText":"Severe respiratory distress ","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Measure saturations in air","title2":"Neutral position &amp; suction visible secretions","title3":"Put on oxygen","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/c80e5c02-79a4-4848-b108-04aa6996d095?height=898&amp;width=1660","fileId":"c80e5c02-79a4-4848-b108-04aa6996d095","filename":"Screen Shot 2016-12-28 at 21.52.40.jpg","size":"183743"},"image2":{"data":"https://webeditor.neotree.org/files/e19cf3b6-b2ce-4dd9-a88d-f2e99f655fda?height=1044&amp;width=1802","fileId":"e19cf3b6-b2ce-4dd9-a88d-f2e99f655fda","filename":"Neutral position 9.jpg","size":"199006"},"image3":{"data":"https://webeditor.neotree.org/files/53bcad22-87d5-479b-b786-bda122ee8b6c?height=452&amp;width=514","fileId":"53bcad22-87d5-479b-b786-bda122ee8b6c","filename":"Screen Shot 2018-10-06 at 19.39.59.png","size":"172101"}}}</v>
       </c>
     </row>
     <row r="8">
@@ -887,7 +887,7 @@
         <v xml:space="preserve">EMERGENCY MANAGEMENT </v>
       </c>
       <c r="D8" t="str">
-        <v>Severe Resp distress1</v>
+        <v xml:space="preserve">Central cyanosis </v>
       </c>
       <c r="E8" t="str">
         <v>management</v>
@@ -920,7 +920,7 @@
         <v/>
       </c>
       <c r="O8" t="str">
-        <v xml:space="preserve">$DangerSigns = 'Grun' </v>
+        <v>$DangerSigns = 'Cyan'</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -941,7 +941,7 @@
         <v/>
       </c>
       <c r="V8" t="str">
-        <v>{"actionText":"Severe respiratory distress ","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Measure saturations in air","title2":"Neutral position &amp; suction visible secretions","title3":"Put on oxygen","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/c80e5c02-79a4-4848-b108-04aa6996d095?height=898&amp;width=1660","fileId":"c80e5c02-79a4-4848-b108-04aa6996d095","filename":"Screen Shot 2016-12-28 at 21.52.40.jpg","size":"183743"},"image2":{"data":"https://webeditor.neotree.org/files/e19cf3b6-b2ce-4dd9-a88d-f2e99f655fda?height=1044&amp;width=1802","fileId":"e19cf3b6-b2ce-4dd9-a88d-f2e99f655fda","filename":"Neutral position 9.jpg","size":"199006"},"image3":{"data":"https://webeditor.neotree.org/files/53bcad22-87d5-479b-b786-bda122ee8b6c?height=452&amp;width=514","fileId":"53bcad22-87d5-479b-b786-bda122ee8b6c","filename":"Screen Shot 2018-10-06 at 19.39.59.png","size":"172101"}}}</v>
+        <v>{"actionText":"CENTRAL CYANOSIS ","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Keep Warm","title2":"Repiratory support ","title3":"Listen for murmurs ","title4":"","text1":"Dry and wrap the baby\n\nPut on a hat\n\nPut the baby under a radiant warmer or resuscitaire \n","text2":"Put on nasal cannula oxygen ","text3":"Use your stethoscope to listen for extra sounds \n\n\nWhen stable if possible refer for ECHOCARDIOGRAM ","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
       </c>
     </row>
     <row r="9">
@@ -955,7 +955,7 @@
         <v xml:space="preserve">EMERGENCY MANAGEMENT </v>
       </c>
       <c r="D9" t="str">
-        <v xml:space="preserve">Central cyanosis </v>
+        <v xml:space="preserve">Convulsions </v>
       </c>
       <c r="E9" t="str">
         <v>management</v>
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="O9" t="str">
-        <v>$DangerSigns = 'Cyan'</v>
+        <v xml:space="preserve">$DangerSigns = 'Convulsions' </v>
       </c>
       <c r="P9" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v/>
       </c>
       <c r="V9" t="str">
-        <v>{"actionText":"CENTRAL CYANOSIS ","contentText":"","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"Keep Warm","title2":"Repiratory support ","title3":"Listen for murmurs ","title4":"","text1":"Dry and wrap the baby\n\nPut on a hat\n\nPut the baby under a radiant warmer or resuscitaire \n","text2":"Put on nasal cannula oxygen ","text3":"Use your stethoscope to listen for extra sounds \n\n\nWhen stable if possible refer for ECHOCARDIOGRAM ","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
+        <v>{"actionText":"CONVULSIONS ","contentText":"Refer to management of convulsions flow chart on wall","infoText":"","title":"EMERGENCY MANAGEMENT ","title1":"1. Airway management &amp; oxygen ","title2":"2. Check blood glucose ","title3":"3. Give anticonvulsants","title4":"","text1":"- Neutral position\n- Check for secretions, suction if needed \n- Put on oxygen","text2":"- If &lt; 45 mg/dl or &lt; 2.5 mmol/L give IV 10% glucose at 2ml/kg\n- If blood glucose monitoring not available give IV 10% glucose at 2ml/kg\n- Do full infection screen\n- If possible take blood for Ca, Mg, U and E’s, FBC","text3":"- Give phenobarbitone 20mg/kg IM \n- Repeat loading dose if necessary\n- If seizures ongoing give Paraldehyde Dose: 0.2 ml/kg IM, 0.4 ml/kg PR \n- If seizures still ongoing - give maintenance phenobarbitone 5mg/kg PO/IM\n\nWhen seizures have stopped and baby stable click the blue arrow to continue ","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":null,"image2":null,"image3":null}}</v>
       </c>
     </row>
     <row r="10">
@@ -1100,7 +1100,7 @@
         <v>DangerSigns2</v>
       </c>
       <c r="G11" t="str">
-        <v xml:space="preserve">Danger Signs 2 </v>
+        <v>Danger Signs 2</v>
       </c>
       <c r="H11" t="str">
         <v>multi_select_option</v>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>[{"value":"Cold","valueLabel":"Trunk feels cold","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PrCRT","valueLabel":"Capillary Refill Time more than 3 seconds ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Wkpulse","valueLabel":"Weak or fast femoral pulses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Cold","valueLabel":"Trunk feels cold","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PrCRT","valueLabel":"Capillary Refill Time more than 3 seconds","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Wkpulse","valueLabel":"Weak or fast, thready femoral pulses","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -2528,7 +2528,7 @@
         <v>HypoSymptoms</v>
       </c>
       <c r="G32" t="str">
-        <v xml:space="preserve">Symptomatic? </v>
+        <v>Symptomatic?</v>
       </c>
       <c r="H32" t="str">
         <v>boolean</v>
@@ -2936,7 +2936,7 @@
         <v>AdmReason</v>
       </c>
       <c r="G38" t="str">
-        <v>Presenting complaint</v>
+        <v>Reason for admission / presenting complaint</v>
       </c>
       <c r="H38" t="str">
         <v>multi_select_option</v>
@@ -3093,7 +3093,7 @@
         <v>$AdmReason = 'OS'</v>
       </c>
       <c r="N40" t="str">
-        <v>[{"value":"AB","valueLabel":"Abscess","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANMA","valueLabel":"Anorectal Malformation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLP","valueLabel":" Cleft lip and palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CY","valueLabel":"Cyst","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ENC","valueLabel":"Encephalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EXP","valueLabel":"Exomphalos/Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FR","valueLabel":"Fractures","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GAS","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HE","valueLabel":"Hernia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HRS","valueLabel":"Hirschprungs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYDR","valueLabel":"Hydrocephalus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPO","valueLabel":"Hypospadias","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MIC","valueLabel":"Microcephaly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SB","valueLabel":"Spinal Bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TAP","valueLabel":"Tallipes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNTE","valueLabel":"Undistended Testicals","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"AB","valueLabel":"Abscess","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ANMA","valueLabel":"Anorectal Malformation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLP","valueLabel":"Cleft lip and palate","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CY","valueLabel":"Cyst","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ENC","valueLabel":"Encephalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EXP","valueLabel":"Exomphalos/Omphalocele","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FR","valueLabel":"Fractures","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GAS","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HE","valueLabel":"Hernia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HRS","valueLabel":"Hirschprungs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYDR","valueLabel":"Hydrocephalus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPO","valueLabel":"Hypospadias","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MIC","valueLabel":"Microcephaly","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SB","valueLabel":"Spinal Bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TAP","valueLabel":"Tallipes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNTE","valueLabel":"Undistended Testicals","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O40" t="str">
         <v>$AdmReason = 'OS'</v>
@@ -3412,7 +3412,7 @@
         <v>DateTimeAdmission</v>
       </c>
       <c r="G45" t="str">
-        <v xml:space="preserve">Date/time admission </v>
+        <v>Date/time admission</v>
       </c>
       <c r="H45" t="str">
         <v>datetime</v>
@@ -3616,7 +3616,7 @@
         <v>MotherSurname</v>
       </c>
       <c r="G48" t="str">
-        <v xml:space="preserve">Mother's Surname </v>
+        <v>Mother's Surname</v>
       </c>
       <c r="H48" t="str">
         <v>string</v>
@@ -3684,7 +3684,7 @@
         <v>BabyFirstName</v>
       </c>
       <c r="G49" t="str">
-        <v xml:space="preserve">Baby's First Name </v>
+        <v>Baby's First Name</v>
       </c>
       <c r="H49" t="str">
         <v>string</v>
@@ -3752,7 +3752,7 @@
         <v>BabySurname</v>
       </c>
       <c r="G50" t="str">
-        <v xml:space="preserve">Baby's Surname </v>
+        <v>Baby's Surname</v>
       </c>
       <c r="H50" t="str">
         <v>string</v>
@@ -3956,7 +3956,7 @@
         <v>DOBTOB</v>
       </c>
       <c r="G53" t="str">
-        <v xml:space="preserve">Date and Time of birth </v>
+        <v>Date and Time of birth</v>
       </c>
       <c r="H53" t="str">
         <v>datetime</v>
@@ -4228,7 +4228,7 @@
         <v>Gestation</v>
       </c>
       <c r="G57" t="str">
-        <v xml:space="preserve">Gestational age at birth (weeks.days)	</v>
+        <v>Gestational age at birth (weeks.days)</v>
       </c>
       <c r="H57" t="str">
         <v>number</v>
@@ -4636,7 +4636,7 @@
         <v>Fontanelle</v>
       </c>
       <c r="G63" t="str">
-        <v xml:space="preserve">Fontanelle </v>
+        <v>Fontanelle</v>
       </c>
       <c r="H63" t="str">
         <v>single_select_option</v>
@@ -4885,7 +4885,7 @@
         <v/>
       </c>
       <c r="V66" t="str">
-        <v>{"actionText":"Assessment of tone","contentText":"Weigh the baby completely naked. While you do this:\n\n1. Check the tone as below\n2. Check the spine for spina bifida \n3. Measure the head circumference\n","infoText":"","title":"Tone","title1":"A = normal, B = hypotonic","title2":"","title3":"","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/84cc2d14-a505-4cb9-ad01-af2bafe8c72c?height=810&amp;width=716","fileId":"84cc2d14-a505-4cb9-ad01-af2bafe8c72c","filename":"Tone jpeg.jpg","size":"133387"},"image2":null,"image3":null}}</v>
+        <v>{"actionText":"Assessment of tone","contentText":"Weigh the baby completely naked. While you do this:\n\n1. Check the tone as below\n2. Check the spine for spina bifida \n3. Measure the head circumference\n","infoText":"","title":"Tone","title1":"A = normal, B = hypotonic","title2":"","title3":"","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/84cc2d14-a505-4cb9-ad01-af2bafe8c72c?height=810&amp;orientation=1&amp;type=jpg&amp;width=716","fileId":"84cc2d14-a505-4cb9-ad01-af2bafe8c72c","filename":"Tone jpeg.jpg","size":"133387"},"image2":null,"image3":null}}</v>
       </c>
     </row>
     <row r="67">
@@ -4997,7 +4997,7 @@
         <v/>
       </c>
       <c r="N68" t="str">
-        <v>[{"value":"Norm","valueLabel":"Normal","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural Tube Defect / Spina Bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OAbn","valueLabel":"Other spinal abnormality ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"Normal","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NTD","valueLabel":"Neural tube defect / spina bifida","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OAbn","valueLabel":"Other spinal abnormality","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -5065,7 +5065,7 @@
         <v/>
       </c>
       <c r="N69" t="str">
-        <v>[{"value":"Alert","valueLabel":"Alert, active, appropriate (normal)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Irrit","valueLabel":"Irritable, hyperalert or inconsolable","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Leth","valueLabel":"Lethargic, quiet, decreased activity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Convulsions","valueLabel":"Seizures, convulsions, or twitchings ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Coma","valueLabel":"Coma (unresponsive)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Alert","valueLabel":"Alert, active, appropriate (normal)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Irrit","valueLabel":"Irritable, hyperalert or inconsolable","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Leth","valueLabel":"Lethargic, quiet, decreased activity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Convulsions","valueLabel":"Seizures, convulsions, or twitchings","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Coma","valueLabel":"Coma (unresponsive)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v/>
       </c>
       <c r="V70" t="str">
-        <v>{"actionText":"THOMPSON SCORE","contentText":"Please complete Thompson score for BA / HIE by assessing posture, moro and grasp as shown below\n","infoText":"","title":"THOMPSON SCORE","title1":"Posture","title2":"","title3":"THOMPSON SCORE (fill in on next page)","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/fbcf627f-4f91-4f4d-b4a5-9751d44e2e20?height=732&amp;width=1058","fileId":"fbcf627f-4f91-4f4d-b4a5-9751d44e2e20","filename":"Posture jpeg.jpg","size":"200569"},"image2":{"data":"https://webeditor.neotree.org/files/f01bde99-8f6b-41f0-a69d-1453ff4e36f0?height=608&amp;width=942","fileId":"f01bde99-8f6b-41f0-a69d-1453ff4e36f0","filename":"Morograsp jpeg.jpg","size":"187244"},"image3":{"data":"https://webeditor.neotree.org/files/4670ebdb-2fd4-435b-a0c7-f012441d0038?height=652&amp;width=1148","fileId":"4670ebdb-2fd4-435b-a0c7-f012441d0038","filename":"Thompson jpeg.jpg","size":"179793"}}}</v>
+        <v>{"actionText":"THOMPSON SCORE","contentText":"Please complete Thompson score for BA / HIE by assessing posture, moro and grasp as shown below\n","infoText":"","title":"THOMPSON SCORE","title1":"Posture","title2":"","title3":"THOMPSON SCORE (fill in on next page)","title4":"","text1":"","text2":"","text3":"","instructions":"","instructions2":"","instructions3":"","instructions4":"","notes":"","refKey":"","images":{"contentTextImage":null,"image1":{"data":"https://webeditor.neotree.org/files/fbcf627f-4f91-4f4d-b4a5-9751d44e2e20?height=732&amp;orientation=1&amp;type=jpg&amp;width=1058","fileId":"fbcf627f-4f91-4f4d-b4a5-9751d44e2e20","filename":"Posture jpeg.jpg","size":"200569"},"image2":{"data":"https://webeditor.neotree.org/files/f01bde99-8f6b-41f0-a69d-1453ff4e36f0?height=608&amp;orientation=1&amp;type=jpg&amp;width=942","fileId":"f01bde99-8f6b-41f0-a69d-1453ff4e36f0","filename":"Morograsp jpeg.jpg","size":"187244"},"image3":{"data":"https://webeditor.neotree.org/files/4670ebdb-2fd4-435b-a0c7-f012441d0038?height=652&amp;orientation=1&amp;type=jpg&amp;width=1148","fileId":"4670ebdb-2fd4-435b-a0c7-f012441d0038","filename":"Thompson jpeg.jpg","size":"179793"}}}</v>
       </c>
     </row>
     <row r="71">
@@ -5928,7 +5928,7 @@
         <v>WOB</v>
       </c>
       <c r="G82" t="str">
-        <v xml:space="preserve">Work of breathing </v>
+        <v>Work of breathing</v>
       </c>
       <c r="H82" t="str">
         <v>single_select_option</v>
@@ -6064,7 +6064,7 @@
         <v>Stethoscope</v>
       </c>
       <c r="G84" t="str">
-        <v xml:space="preserve">Stethoscope </v>
+        <v>Stethoscope</v>
       </c>
       <c r="H84" t="str">
         <v>boolean</v>
@@ -6153,7 +6153,7 @@
         <v>$Stethoscope = true</v>
       </c>
       <c r="N85" t="str">
-        <v>[{"value":"Clear","valueLabel":"Chest is clear","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"UeqAE","valueLabel":"Unequal air entry","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UniCr","valueLabel":"Unilateral crackles ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UniWh","valueLabel":"Unilateral wheeze","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BilatCr","valueLabel":"Bilateral crackles/wheeze","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Strid","valueLabel":"Stridor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Clear","valueLabel":"Chest is clear","disabledOtherOptionsIfSelected":true,"forbidWIth":[]},{"value":"UeqAE","valueLabel":"Unequal air entry","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UniCr","valueLabel":"Unilateral crackles","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UniWh","valueLabel":"Unilateral wheeze","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BilatCr","valueLabel":"Bilateral crackles/wheeze","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Strid","valueLabel":"Stridor","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O85" t="str">
         <v>$Stethoscope = true</v>
@@ -6469,7 +6469,7 @@
         <v>multi_select</v>
       </c>
       <c r="F90" t="str">
-        <v>SignsDehydrations</v>
+        <v>DehydraSigns</v>
       </c>
       <c r="G90" t="str">
         <v>Signs of Dehydration</v>
@@ -6493,7 +6493,7 @@
         <v>$AgeA = 'N' or ($AgeCat = 'NB48' or $AgeCat = 'INF72' or $AgeCat = 'INF')</v>
       </c>
       <c r="N90" t="str">
-        <v>[{"value":"PSP","valueLabel":"Prolonged skin pinch","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DMM","valueLabel":"Dry Mucous Membranes ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SE","valueLabel":"Sunken Eyes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"PSP","valueLabel":"Prolonged skin pinch ( &gt; 2seconds)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DMM","valueLabel":"Dry Mucous Membranes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SE","valueLabel":"Sunken Eyes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O90" t="str">
         <v>$AgeA = 'N' or ($AgeCat = 'NB48' or $AgeCat = 'INF72' or $AgeCat = 'INF')</v>
@@ -7016,7 +7016,7 @@
         <v>Anus2</v>
       </c>
       <c r="G98" t="str">
-        <v xml:space="preserve">Anus </v>
+        <v>Anus</v>
       </c>
       <c r="H98" t="str">
         <v>single_select_option</v>
@@ -7785,7 +7785,7 @@
         <v/>
       </c>
       <c r="N109" t="str">
-        <v>[{"value":"DIB","valueLabel":"Fast or laboured breathing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NBr","valueLabel":"Noisy Breathing ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cough","valueLabel":"Cough","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Apn","valueLabel":"Apnoea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BE","valueLabel":"Blue episodes ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"DIB","valueLabel":"Fast or laboured breathing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NBr","valueLabel":"Noisy Breathing","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Cough","valueLabel":"Cough","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Apn","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BE","valueLabel":"Blue episodes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -7853,7 +7853,7 @@
         <v>$RespSR != 'Norm'</v>
       </c>
       <c r="N110" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 -3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O110" t="str">
         <v>$RespSR != 'Norm'</v>
@@ -7989,7 +7989,7 @@
         <v>$Vomiting != 'Norm'</v>
       </c>
       <c r="N112" t="str">
-        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"More than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"L24","valueLabel":"Less than 24hrs ago","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"1t2d","valueLabel":"1 - 2 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"2t3d","valueLabel":"2 - 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"M3d","valueLabel":"more than 3 days","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O112" t="str">
         <v>$Vomiting != 'Norm'</v>
@@ -8057,7 +8057,7 @@
         <v/>
       </c>
       <c r="N113" t="str">
-        <v>[{"value":"NFY","valueLabel":"Has not had a breast feed yet ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feeding normally","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BFH","valueLabel":"Needs help breast feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CUPEBM","valueLabel":"Cup/ Spoon feeds with breast milk","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CUPFOR","valueLabel":"Cup/ Spoon feeds with formula","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGEBM","valueLabel":"NG feeds with EBM","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGFORM","valueLabel":"NG feeds with formula","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IVF","valueLabel":"Intravenous fluids","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"NFY","valueLabel":"Has not had a breast feed yet","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BF","valueLabel":"Breast feeding normally","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BFH","valueLabel":"Needs help breast feeding","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CUPEBM","valueLabel":"Cup/ Spoon feeds with breast milk","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CUPFOR","valueLabel":"Cup/ Spoon feeds with formula","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGEBM","valueLabel":"NG feeds with EBM","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NGFORM","valueLabel":"NG feeds with formula","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"IVF","valueLabel":"Intravenous fluids","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -8376,7 +8376,7 @@
         <v>SRNeuroOther</v>
       </c>
       <c r="G118" t="str">
-        <v>Any other symptoms?</v>
+        <v>Other Neuro symptoms?</v>
       </c>
       <c r="H118" t="str">
         <v>multi_select_option</v>
@@ -8397,7 +8397,7 @@
         <v/>
       </c>
       <c r="N118" t="str">
-        <v>[{"value":"Convulsions","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CL","valueLabel":"Crying less than usual","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CrM","valueLabel":"Crying more than usual","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fl","valueLabel":"Floppy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"St","valueLabel":"Stiff neck or limbs ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Convulsions","valueLabel":"Convulsions","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CL","valueLabel":"Crying less than usual","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CrM","valueLabel":"Crying more than usual","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Fl","valueLabel":"Floppy","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"St","valueLabel":"Stiff neck or limbs","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O118" t="str">
         <v/>
@@ -8669,7 +8669,7 @@
         <v>$InOrOut = false</v>
       </c>
       <c r="N122" t="str">
-        <v>[{"value":"H","valueLabel":"Home - Self Referral","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Other facility","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped Baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"H","valueLabel":"Home - Self Referral","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"F","valueLabel":"Other facility","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DU","valueLabel":"Dumped baby","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O122" t="str">
         <v>$InOrOut = false</v>
@@ -8784,7 +8784,7 @@
         <v>OtherReferralFacility</v>
       </c>
       <c r="G124" t="str">
-        <v xml:space="preserve">Name of Facility </v>
+        <v>Name of Facility</v>
       </c>
       <c r="H124" t="str">
         <v>string</v>
@@ -8941,7 +8941,7 @@
         <v>$BirthPlaceSame = false or ($InOrOut = false and $ReferredFrom2 = 'H')</v>
       </c>
       <c r="N126" t="str">
-        <v>[{"value":"Hosp","valueLabel":"Hospital ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HC","valueLabel":"Health Centre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born on the way to hospital (in transit)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Home","valueLabel":"Home","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Hosp","valueLabel":"Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HC","valueLabel":"Health Centre","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BBA","valueLabel":"Born on the way to hospital (in transit)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Home","valueLabel":"Home","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O126" t="str">
         <v>$BirthPlaceSame = false or ($InOrOut = false and $ReferredFrom2 = 'H')</v>
@@ -9009,7 +9009,7 @@
         <v>$BirthPlaceSame = false and $PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
       </c>
       <c r="N127" t="str">
-        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lum","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu community hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ded","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"A25","valueLabel":"Area 25 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Lum","valueLabel":"Lumbadzi HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Bwai","valueLabel":"Bwaila Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kab","valueLabel":"Kabudula rural hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mit","valueLabel":"Mitundu Community Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mchi","valueLabel":"Mchinji District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Sal","valueLabel":"Salima District hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Dowa","valueLabel":"Dowa District Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CLI","valueLabel":"Child Legacy International Hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kaw","valueLabel":"Kawale HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"A18","valueLabel":"Area 18 HC","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ded","valueLabel":"Dedza district hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Kas","valueLabel":"Kasungu District hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Nkhot","valueLabel":"Nkhotakota District hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Mzuzu","valueLabel":"Mzuzu central hospital","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O127" t="str">
         <v>$BirthPlaceSame = false and $PlaceBirth = 'Hosp' or $PlaceBirth = 'HC'</v>
@@ -9056,7 +9056,7 @@
         <v>OtherBirthFacility</v>
       </c>
       <c r="G128" t="str">
-        <v xml:space="preserve">Name of facility: </v>
+        <v>Name of facility:</v>
       </c>
       <c r="H128" t="str">
         <v>string</v>
@@ -9145,7 +9145,7 @@
         <v/>
       </c>
       <c r="N129" t="str">
-        <v>[{"value":"WR","valueLabel":"Wrapped"},{"value":"KMC","valueLabel":"Kangaroo Mother Care"},{"value":"MobInc","valueLabel":"Mobile Incubator"},{"value":"Norm","valueLabel":"None"}]</v>
+        <v>[{"value":"WR","valueLabel":"Wrapped"},{"value":"KMC","valueLabel":"Kangaroo Mother Care"},{"value":"MobInc","valueLabel":"Mobile Incubator"},{"value":"Norm","valueLabel":"NONE"}]</v>
       </c>
       <c r="O129" t="str">
         <v>$AdmittedFrom = 'LW' or $AdmittedFrom = 'TH'</v>
@@ -9961,7 +9961,7 @@
         <v>$ParityDeadChildren &gt; 0</v>
       </c>
       <c r="N141" t="str">
-        <v>[{"value":"AB","valueLabel":"Abortion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Aneamia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CON","valueLabel":"Congenital Anomalies","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EPM","valueLabel":"Extreme Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPO","valueLabel":"Hypoglycemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PNE","valueLabel":"Pnemonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SE","valueLabel":"Sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHIE","valueLabel":"Severe HIE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SMA","valueLabel":"Severe Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TE","valueLabel":"Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"AB","valueLabel":"Abortion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Aneamia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CON","valueLabel":"Congenital Anomalies","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EPM","valueLabel":"Extreme Prematurity","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PNE","valueLabel":"Pnemonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SE","valueLabel":"Sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SHIE","valueLabel":"Severe HIE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SMA","valueLabel":"Severe Malaria","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TE","valueLabel":"Tetanus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O141" t="str">
         <v>$ParityDeadChildren &gt; 0</v>
@@ -10212,7 +10212,7 @@
         <v>EthnicityOther</v>
       </c>
       <c r="G145" t="str">
-        <v xml:space="preserve">If other, what is your ethnicity? </v>
+        <v>If other, what is your ethnicity?</v>
       </c>
       <c r="H145" t="str">
         <v>string</v>
@@ -10348,7 +10348,7 @@
         <v>TribeOther</v>
       </c>
       <c r="G147" t="str">
-        <v xml:space="preserve">If other, which tribe? </v>
+        <v>If other, which tribe?</v>
       </c>
       <c r="H147" t="str">
         <v>string</v>
@@ -10437,7 +10437,7 @@
         <v>$AdmReason != 'DU'</v>
       </c>
       <c r="N148" t="str">
-        <v>[{"value":"A","valueLabel":"Anglican (Christian protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AOG","valueLabel":"Assemblies of god","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CCAP","valueLabel":"Church of Central Africa (CCAP)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CFC","valueLabel":"Calvary Family Church ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"COC","valueLabel":"Church of Christ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BB","valueLabel":"Bible Believers ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian) ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ECG","valueLabel":"Enlightened Christian Gathering (ECG)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehover's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LW","valueLabel":"Living Waters","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AC","valueLabel":"African Church","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"A","valueLabel":"Anglican (Christian protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AOG","valueLabel":"Assemblies of god","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Ba","valueLabel":"Baptist (Christian Protestant)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CCAP","valueLabel":"Church of Central Africa (CCAP)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CFC","valueLabel":"Calvary Family Church","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"COC","valueLabel":"Church of Christ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CP","valueLabel":"Other Christian Protestant","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BB","valueLabel":"Bible Believers","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RC","valueLabel":"Roman Catholic (Christian)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ECG","valueLabel":"Enlightened Christian Gathering (ECG)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MU","valueLabel":"Muslim","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"P","valueLabel":"Prespyterian","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SDA","valueLabel":"Seventh Day Adventist (SDA)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"JW","valueLabel":"Jehover's Witness","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LW","valueLabel":"Living Waters","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Z","valueLabel":"Zion","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AG","valueLabel":"Agnostic","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ATH","valueLabel":"Atheist","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AC","valueLabel":"African Church","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O148" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -10700,10 +10700,10 @@
         <v/>
       </c>
       <c r="K152" t="str">
+        <v>No</v>
+      </c>
+      <c r="L152" t="str">
         <v>Yes</v>
-      </c>
-      <c r="L152" t="str">
-        <v>No</v>
       </c>
       <c r="M152" t="str">
         <v/>
@@ -10836,7 +10836,7 @@
         <v/>
       </c>
       <c r="K154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L154" t="str">
         <v>No</v>
@@ -10904,7 +10904,7 @@
         <v/>
       </c>
       <c r="K155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L155" t="str">
         <v>No</v>
@@ -10972,7 +10972,7 @@
         <v/>
       </c>
       <c r="K156" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L156" t="str">
         <v>No</v>
@@ -11504,7 +11504,7 @@
         <v>ANVDRL</v>
       </c>
       <c r="G164" t="str">
-        <v xml:space="preserve">Syphilis test? </v>
+        <v>Syphilis test?</v>
       </c>
       <c r="H164" t="str">
         <v>single_select_option</v>
@@ -11729,7 +11729,7 @@
         <v/>
       </c>
       <c r="N167" t="str">
-        <v>[{"value":"P","valueLabel":"POSITIVE"},{"value":"N","valueLabel":"NEGATIVE"},{"value":"U","valueLabel":"UNKOWN"}]</v>
+        <v>[{"value":"P","valueLabel":"Positive"},{"value":"N","valueLabel":"Negative"},{"value":"U","valueLabel":"UNKOWN"}]</v>
       </c>
       <c r="O167" t="str">
         <v>$ANVDRL = 'Y'</v>
@@ -11980,7 +11980,7 @@
         <v>TypeSTD</v>
       </c>
       <c r="G171" t="str">
-        <v xml:space="preserve">What was this STD? </v>
+        <v>What was this STD?</v>
       </c>
       <c r="H171" t="str">
         <v>string</v>
@@ -12524,7 +12524,7 @@
         <v>ProbsLab</v>
       </c>
       <c r="G179" t="str">
-        <v xml:space="preserve">Problems in Labour </v>
+        <v>Problems in Labour</v>
       </c>
       <c r="H179" t="str">
         <v>multi_select_option</v>
@@ -12545,7 +12545,7 @@
         <v>$AdmReason != 'DU'</v>
       </c>
       <c r="N179" t="str">
-        <v>[{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios ","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SVB","valueLabel":"Significant Vaginal Bleeding (APH - Antipartum Haemorrhage)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Conv","valueLabel":"Convulsions / Eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Olig","valueLabel":"Oligohydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Pre","valueLabel":"Pre-eclampsia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Poly","valueLabel":"Polyhydramnios","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SVB","valueLabel":"Significant Vaginal Bleeding (APH - Antipartum Haemorrhage)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TU","valueLabel":"Tuberculosis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O179" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -12796,7 +12796,7 @@
         <v>RFSepsis</v>
       </c>
       <c r="G183" t="str">
-        <v xml:space="preserve">Risk Factors for Sepsis </v>
+        <v>Risk Factors for Sepsis</v>
       </c>
       <c r="H183" t="str">
         <v>multi_select_option</v>
@@ -12885,7 +12885,7 @@
         <v/>
       </c>
       <c r="N184" t="str">
-        <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"Unk","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"Vertex","valueLabel":"Vertex"},{"value":"Brow","valueLabel":"Brow"},{"value":"Breech","valueLabel":"Breech"},{"value":"Face","valueLabel":"Face"},{"value":"UNK","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O184" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -13157,7 +13157,7 @@
         <v>$AdmReason != 'DU'</v>
       </c>
       <c r="N188" t="str">
-        <v>[{"value":"Yes","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"No","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Yes","valueLabel":"Yes","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"No","valueLabel":"No","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O188" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -13225,7 +13225,7 @@
         <v xml:space="preserve">$MecPresent = 'Yes' </v>
       </c>
       <c r="N189" t="str">
-        <v>[{"value":"Thick","valueLabel":"Thick","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Thin","valueLabel":"Thin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Thick","valueLabel":"Thick","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Thin","valueLabel":"Thin","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O189" t="str">
         <v xml:space="preserve">$MecPresent = 'Yes' </v>
@@ -13272,7 +13272,7 @@
         <v>CryBirth</v>
       </c>
       <c r="G190" t="str">
-        <v xml:space="preserve">Did the baby cry straight after birth? </v>
+        <v>Did the baby cry straight after birth?</v>
       </c>
       <c r="H190" t="str">
         <v>dropdown</v>
@@ -13340,7 +13340,7 @@
         <v>Apgar1</v>
       </c>
       <c r="G191" t="str">
-        <v xml:space="preserve">Apgar Score at 1 min </v>
+        <v>Apgar Score at 1 min</v>
       </c>
       <c r="H191" t="str">
         <v>number</v>
@@ -13565,7 +13565,7 @@
         <v>$AdmReason != 'DU'</v>
       </c>
       <c r="N194" t="str">
-        <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Unk","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
+        <v>[{"value":"Stim","valueLabel":"Stimulation","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Suc","valueLabel":"Suctioning","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"O2","valueLabel":"Oxygen","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BVM","valueLabel":"Bag Valve Mask Ventilation (BVM)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CPR","valueLabel":"Cardio Pulmonary Resuscitation (CPR)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":true,"forbidWIth":[]}]</v>
       </c>
       <c r="O194" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -13633,7 +13633,7 @@
         <v/>
       </c>
       <c r="N195" t="str">
-        <v>[{"value":"Kn","valueLabel":"Known"},{"value":"Unk","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"Kn","valueLabel":"Known"},{"value":"UNK","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O195" t="str">
         <v>$Resus = 'CPR'</v>
@@ -13905,7 +13905,7 @@
         <v>$VitK = 'N'</v>
       </c>
       <c r="N199" t="str">
-        <v>[{"value":"U","valueLabel":"Unavailable"},{"value":"R","valueLabel":"Refused"},{"value":"Unk","valueLabel":"Unknown"}]</v>
+        <v>[{"value":"U","valueLabel":"Unavailable"},{"value":"R","valueLabel":"Refused"},{"value":"UNK","valueLabel":"Unknown"}]</v>
       </c>
       <c r="O199" t="str">
         <v>$AdmReason != 'DU'</v>
@@ -14564,7 +14564,7 @@
         <v>MedAdm</v>
       </c>
       <c r="G209" t="str">
-        <v xml:space="preserve">Other medication to be given on admission </v>
+        <v>Other medication to be given on admission</v>
       </c>
       <c r="H209" t="str">
         <v>multi_select</v>
@@ -15265,7 +15265,7 @@
         <v/>
       </c>
       <c r="N219" t="str">
-        <v>[{"value":"BERN","valueLabel":"Bernadette Nyambo"},{"value":"BRNA","valueLabel":"Bridget Namanya"},{"value":"DAMU","valueLabel":"Daniel Mughyombe"},{"value":"FUST","valueLabel":"Funnie Steven"},{"value":"GLZA","valueLabel":"Gloria Zailani"},{"value":"TANY","valueLabel":"Tamara Nyasulu"},{"value":"LIPH","valueLabel":"Linna Phiri"},{"value":"MPGR","valueLabel":"Mphatso Grant"},{"value":"PRDI","valueLabel":"Precious Dinga"},{"value":"PRMA","valueLabel":"Prince Magawa"},{"value":"RHCH","valueLabel":"Rhoda Chifisi"},{"value":"PAKA","valueLabel":"Pamela Kawaga"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"WAKU","valueLabel":"Watson Kumwenda"},{"value":"BRMH","valueLabel":"Brandina Mhlanga"},{"value":"OMMA","valueLabel":"Omega Makonde"},{"value":"PECH","valueLabel":"Peter Chirwa"},{"value":"VEKU","valueLabel":"Veronica Kunkeani"},{"value":"TAGA","valueLabel":"Tadala Gamadzi"},{"value":"INNA","valueLabel":"Innocent Namate"},{"value":"SANK","valueLabel":"Samantha Nkochi"},{"value":"TENGO","valueLabel":"Temwa Ngoma"},{"value":"EDCI","valueLabel":"Edith Chiwanda"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"BERN","valueLabel":"Bernadette Nyambo"},{"value":"BRNA","valueLabel":"Bridget Namanya"},{"value":"DAMU","valueLabel":"Daniel Mughyombe"},{"value":"FUST","valueLabel":"Funnie Steven"},{"value":"GLZA","valueLabel":"Gloria Zailani"},{"value":"TANY","valueLabel":"Tamara Nyasulu"},{"value":"LIPH","valueLabel":"Linna Phiri"},{"value":"MPGR","valueLabel":"Mphatso Grant"},{"value":"PRDI","valueLabel":"Precious Dinga"},{"value":"PRMA","valueLabel":"Prince Magawa"},{"value":"RHCH","valueLabel":"Rhoda Chifisi"},{"value":"PAKA","valueLabel":"Pamela Kawaga"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"WAKU","valueLabel":"Watson Kumwenda"},{"value":"BRMH","valueLabel":"Brandina Mhlanga"},{"value":"OMMA","valueLabel":"Omega Makonde"},{"value":"PECH","valueLabel":"Peter Chirwa"},{"value":"VEKU","valueLabel":"Veronica Kunkeani"},{"value":"TAGA","valueLabel":"Tadala Gamadzi"},{"value":"INNA","valueLabel":"Innocent Namate"},{"value":"SANK","valueLabel":"Samantha Nkochi"},{"value":"TENGO","valueLabel":"Temwa Ngoma"},{"value":"EDCI","valueLabel":"Edith Chiwanda"},{"value":"FNST","valueLabel":"Fannie Steven"},{"value":"TENJ","valueLabel":"Tendai Njeula"},{"value":"GLNK","valueLabel":"Gloria Nkhonjera"},{"value":"ELMU","valueLabel":"Eleanor Muhemera"},{"value":"NEKA","valueLabel":"Nenenji Kachiwiya"},{"value":"PENI","valueLabel":"Pemphero Nishiya"},{"value":"MENG","valueLabel":"Mercy Ngulume"},{"value":"GEKO","valueLabel":"Getrude Kondwani"},{"value":"DAKA","valueLabel":"Dalitso Kantwanje"},{"value":"CYMA","valueLabel":"Cynthia Matemba"},{"value":"EDCH","valueLabel":"Edith Chiwanda"},{"value":"LEKA","valueLabel":"Lexina Kamphanje"},{"value":"TAWH","valueLabel":"Tamandani Whayo"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O219" t="str">
         <v/>
@@ -15607,7 +15607,7 @@
         <v>Possible Meconium Aspiration</v>
       </c>
       <c r="H2" t="str">
-        <v>2516</v>
+        <v>2984</v>
       </c>
       <c r="I2" t="str">
         <v>editor</v>
@@ -15622,7 +15622,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>[{"expression":"$MecPresent = 'Yes'","name":"Meconium at delivery","type":"risk","weight":"1.0","position":1,"symptomId":"4e3a069f-ec92-4059-8bcc-6fb6abd150ad","printable":true,"keyId":"3bda99f3-9342-4707-ac47-db2d249d2778"},{"expression":"$Umbilicus = 'Mec'","name":"Mec stained umbilicus","type":"risk","weight":"1.0","position":2,"symptomId":"7cf67cde-02cd-4e59-bda4-8f7b5b1460e6","printable":true,"keyId":"43a71eee-031a-41db-9fc8-9cdd436fa0b1"},{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":3,"symptomId":"cf34fd3a-54ab-42fe-bc08-1a6f7d81ff2f","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183"},{"expression":"$RR &gt; 80","name":"Tachynoea &gt; 80","type":"sign","weight":"1.0","position":4,"symptomId":"b11e5acd-ec89-4d67-b2c3-2e47a85a39b8","printable":true,"keyId":"3b4966d1-c75b-4163-9fb2-7d6f83d3a54c"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing ","type":"sign","weight":"1.0","position":5,"symptomId":"5d81661c-64fe-42fc-ade1-87ca5c5a5cc7","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":6,"symptomId":"335de710-27c5-4d56-bf70-10b114cff8ff","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904"},{"expression":"$SatsAir &lt; 90","name":"Saturations in air &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"ef84a975-4f0b-4c58-ab97-f2f5aceaaf05","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in oxygen &lt; 90","type":"sign","weight":"1.0","position":8,"symptomId":"5b14bdf0-c450-46b0-ab54-408fb070cdd5","printable":true,"keyId":"ff5acafd-9c6f-4cee-b3b4-fd78ef191f91"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of work of breathing","type":"sign","weight":"1.0","position":9,"symptomId":"a2c73691-a689-4356-b476-09f9b4f3888d","printable":true,"keyId":"2fccdd60-be7c-41bf-93ce-462f509f2744"},{"expression":"$ChestAusc = 'BilatCr'","name":"Bilateral crackles or wheeze","type":"sign","weight":"1.0","position":10,"symptomId":"70e53a86-bdcd-486b-8797-08cf8c97fa5f","printable":true,"keyId":"67492f9a-2bf1-410e-9f3f-12d350a689bb"},{"expression":"$PassedMec = 'MecLiq'","name":"Passed Mec in liquor","type":"risk","weight":"1.0","position":11,"symptomId":"2ea4b456-87c7-4f9a-a89f-d4b9ae98aae9","printable":true,"keyId":"317a426e-0f47-4cdc-bde9-63cb11783610"}]</v>
+        <v>[{"expression":"$MecPresent = 'Yes'","name":"Meconium at delivery","type":"risk","weight":"1.0","position":1,"symptomId":"4e3a069f-ec92-4059-8bcc-6fb6abd150ad","printable":true,"keyId":"3bda99f3-9342-4707-ac47-db2d249d2778","key":"Meconium at delivery"},{"expression":"$Umbilicus = 'Mec'","name":"Mec stained umbilicus","type":"risk","weight":"1.0","position":2,"symptomId":"7cf67cde-02cd-4e59-bda4-8f7b5b1460e6","printable":true,"keyId":"43a71eee-031a-41db-9fc8-9cdd436fa0b1","key":"Mec stained umbilicus"},{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":3,"symptomId":"cf34fd3a-54ab-42fe-bc08-1a6f7d81ff2f","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183","key":"Grunting or severe recessions"},{"expression":"$RR &gt; 80","name":"Tachynoea &gt; 80","type":"sign","weight":"1.0","position":4,"symptomId":"b11e5acd-ec89-4d67-b2c3-2e47a85a39b8","printable":true,"keyId":"3b4966d1-c75b-4163-9fb2-7d6f83d3a54c","key":"Tachynoea &gt; 80"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":5,"symptomId":"5d81661c-64fe-42fc-ade1-87ca5c5a5cc7","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f","key":"History of fast or laboured breathing"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":6,"symptomId":"335de710-27c5-4d56-bf70-10b114cff8ff","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904","key":"History of noisy breathing"},{"expression":"$SatsAir &lt; 90","name":"Saturations in air &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"ef84a975-4f0b-4c58-ab97-f2f5aceaaf05","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2","key":"Saturations in air &lt; 90"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in oxygen &lt; 90","type":"sign","weight":"1.0","position":8,"symptomId":"5b14bdf0-c450-46b0-ab54-408fb070cdd5","printable":true,"keyId":"ff5acafd-9c6f-4cee-b3b4-fd78ef191f91","key":"Saturations in oxygen &lt; 90"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of work of breathing","type":"sign","weight":"1.0","position":9,"symptomId":"a2c73691-a689-4356-b476-09f9b4f3888d","printable":true,"keyId":"2fccdd60-be7c-41bf-93ce-462f509f2744","key":"Any severity of work of breathing"},{"expression":"$ChestAusc = 'BilatCr'","name":"Bilateral crackles or wheeze","type":"sign","weight":"1.0","position":10,"symptomId":"70e53a86-bdcd-486b-8797-08cf8c97fa5f","printable":true,"keyId":"67492f9a-2bf1-410e-9f3f-12d350a689bb","key":"Bilateral crackles or wheeze"},{"expression":"$PassedMec = 'MecLiq'","name":"Passed Mec in liquor","type":"risk","weight":"1.0","position":11,"symptomId":"2ea4b456-87c7-4f9a-a89f-d4b9ae98aae9","printable":true,"keyId":"317a426e-0f47-4cdc-bde9-63cb11783610","key":"Passed Mec in liquor"}]</v>
       </c>
       <c r="N2" t="str" xml:space="preserve">
         <v xml:space="preserve">Think - is this really Meconium aspiration?
@@ -15696,7 +15696,7 @@
         <v>Suspected neonatal sepsis</v>
       </c>
       <c r="H3" t="str">
-        <v>2517</v>
+        <v>2985</v>
       </c>
       <c r="I3" t="str">
         <v>editor</v>
@@ -15799,7 +15799,7 @@
         <v>Difficulty Feeding</v>
       </c>
       <c r="H4" t="str">
-        <v>2518</v>
+        <v>2986</v>
       </c>
       <c r="I4" t="str">
         <v>editor</v>
@@ -15814,7 +15814,7 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>[{"expression":"$FeedingReview = 'BFH'","name":"Needs help breast feeding","type":"sign","weight":"1.0","position":1,"symptomId":"11216ef5-397c-4ff5-97c5-2aa4d327c1dd","printable":true,"keyId":"a66b249f-6f38-436b-88f2-00c7b4aeee4a"},{"expression":"$FeedingReview = 'CSP'","name":"Needs cup or spoon feeding","type":"sign","weight":"1.0","position":2,"symptomId":"45bedffd-c6f2-4c38-a646-80dd766df591","printable":true,"keyId":"da83a89b-3dc9-41df-a6d5-b7459cebe38e"},{"expression":"$FeedingReview = 'NG'","name":"Refusing all feeds: needs NG","type":"sign","weight":"1.0","position":3,"symptomId":"4bf921bd-56f4-4d5e-952c-28c9311721e3","printable":true,"keyId":"f86d965f-0ca1-4f2d-a17b-7474bcdfbe0b"},{"expression":"$FeedingReview = 'IVF'","name":"Requires IV fluids","type":"sign","weight":"1.0","position":4,"symptomId":"f0315126-f523-4425-8aef-b10a5cbb952d","printable":true,"keyId":"a9b31315-4edd-48b1-8cd3-dae3823536af"},{"expression":"$SuckReflex = 'Absent'","name":"Absent suck","type":"sign","weight":"1.0","position":5,"symptomId":"37d2fe1f-ddbe-4174-8dbb-fa9dcb1a2a9b","printable":true,"keyId":"3e02408c-e607-4169-bd0c-164dd39490d0"}]</v>
+        <v>[{"expression":"$FeedingReview = 'BFH'","name":"Needs help breast feeding","type":"sign","weight":"1.0","position":1,"symptomId":"11216ef5-397c-4ff5-97c5-2aa4d327c1dd","printable":true,"keyId":"a66b249f-6f38-436b-88f2-00c7b4aeee4a","key":"Needs help breast feeding"},{"expression":"$FeedingReview = 'CSP'","name":"Needs cup or spoon feeding","type":"sign","weight":"1.0","position":2,"symptomId":"45bedffd-c6f2-4c38-a646-80dd766df591","printable":true,"keyId":"da83a89b-3dc9-41df-a6d5-b7459cebe38e","key":"Needs cup or spoon feeding"},{"expression":"$FeedingReview = 'NG'","name":"Refusing all feeds: needs NG","type":"sign","weight":"1.0","position":3,"symptomId":"4bf921bd-56f4-4d5e-952c-28c9311721e3","printable":true,"keyId":"f86d965f-0ca1-4f2d-a17b-7474bcdfbe0b","key":"Refusing all feeds: needs NG"},{"expression":"$FeedingReview = 'IVF'","name":"Requires IV fluids","type":"sign","weight":"1.0","position":4,"symptomId":"f0315126-f523-4425-8aef-b10a5cbb952d","printable":true,"keyId":"a9b31315-4edd-48b1-8cd3-dae3823536af","key":"Requires IV fluids"},{"expression":"$SuckReflex = 'Absent'","name":"Absent suck","type":"sign","weight":"1.0","position":5,"symptomId":"37d2fe1f-ddbe-4174-8dbb-fa9dcb1a2a9b","printable":true,"keyId":"3e02408c-e607-4169-bd0c-164dd39490d0","key":"Absent suck"}]</v>
       </c>
       <c r="N4" t="str" xml:space="preserve">
         <v xml:space="preserve">Baby stable breathing &lt;60bpm
@@ -15879,7 +15879,7 @@
         <v>Dehydration</v>
       </c>
       <c r="H5" t="str">
-        <v>2519</v>
+        <v>2987</v>
       </c>
       <c r="I5" t="str">
         <v>editor</v>
@@ -15894,7 +15894,7 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>[{"expression":"$SignsDehydrations = 'PSP'","name":"Prolonged skin pinch","type":"sign","weight":"1.0","position":1,"symptomId":"0a180cff-303a-4c03-8b56-43b0105b91af","printable":true,"keyId":"9159f93f-1dac-4343-bcdb-35db47569ade"},{"expression":"$SignsDehydrations = 'DMM'","name":"Dry Mucous Membranes ","type":"sign","weight":"1.0","position":2,"symptomId":"ce994d42-b614-40d7-b3e1-038e772e0afa","printable":true,"keyId":"c73e08c5-a5bf-4bae-8904-a0503b76d184"},{"expression":"$SignsDehydrations = 'SE'","name":"Sunken eyes","type":"sign","weight":"1.0","position":3,"symptomId":"ce7e2d95-0257-4aa1-a04e-f83689e3dc07","printable":true,"keyId":"026555d2-aba2-461d-b56e-86ac13ee4121"},{"expression":"$Fontanelle = 'Sunk'","name":"Fontanelle Sunken","type":"sign","weight":"1.0","position":4,"symptomId":"d655b4de-34f4-4799-8306-b84d5c625cff","printable":true,"keyId":"f8725ec4-2fdb-49d5-bf56-935d73a6115d"}]</v>
+        <v>[{"expression":"$SignsDehydrations = 'PSP'","name":"Prolonged skin pinch","type":"sign","weight":"1.0","position":1,"symptomId":"0a180cff-303a-4c03-8b56-43b0105b91af","printable":true,"keyId":"9159f93f-1dac-4343-bcdb-35db47569ade","key":"Prolonged skin pinch"},{"expression":"$SignsDehydrations = 'DMM'","name":"Dry Mucous Membranes","type":"sign","weight":"1.0","position":2,"symptomId":"ce994d42-b614-40d7-b3e1-038e772e0afa","printable":true,"keyId":"c73e08c5-a5bf-4bae-8904-a0503b76d184","key":"Dry Mucous Membranes"},{"expression":"$SignsDehydrations = 'SE'","name":"Sunken eyes","type":"sign","weight":"1.0","position":3,"symptomId":"ce7e2d95-0257-4aa1-a04e-f83689e3dc07","printable":true,"keyId":"026555d2-aba2-461d-b56e-86ac13ee4121","key":"Sunken eyes"},{"expression":"$Fontanelle = 'Sunk'","name":"Sunken Fontanelle","type":"sign","weight":"1.0","position":4,"symptomId":"d655b4de-34f4-4799-8306-b84d5c625cff","printable":true,"key":"SunkFont"}]</v>
       </c>
       <c r="N5" t="str">
         <v xml:space="preserve">Refer to WHO plan A, B or C as below: </v>
@@ -15956,7 +15956,7 @@
         <v>Congenital Heart Disease</v>
       </c>
       <c r="H6" t="str">
-        <v>2520</v>
+        <v>2988</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -16042,7 +16042,7 @@
         <v>Anaemia</v>
       </c>
       <c r="H7" t="str">
-        <v>2521</v>
+        <v>2989</v>
       </c>
       <c r="I7" t="str">
         <v>editor</v>
@@ -16057,7 +16057,7 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v>[{"expression":"$Colour = 'White'","name":"White colour","type":"sign","weight":"1.0","position":1,"symptomId":"bfc579dc-8647-49ff-afde-e827f8882e86","printable":true,"keyId":"da111773-64fd-4a71-b08f-463ad9659c9f"},{"expression":"$FeFo = 'NONE'","name":"No Mat FeFo","type":"sign","weight":"1.0","position":2,"symptomId":"fd437003-88c2-401d-b181-e3342a813898","printable":true,"keyId":"22aab740-e7b9-49a3-a47b-26c6c573245b"}]</v>
+        <v>[{"expression":"$Colour = 'White'","name":"White colour","type":"sign","weight":"1.0","position":1,"symptomId":"bfc579dc-8647-49ff-afde-e827f8882e86","printable":true,"keyId":"da111773-64fd-4a71-b08f-463ad9659c9f","key":"White colour"},{"expression":"$FeFo = 'NONE'","name":"No Mat FeFo","type":"sign","weight":"1.0","position":2,"symptomId":"fd437003-88c2-401d-b181-e3342a813898","printable":true,"keyId":"22aab740-e7b9-49a3-a47b-26c6c573245b","key":"No Mat FeFo"}]</v>
       </c>
       <c r="N7" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Limit blood loss and supportive care
@@ -16127,7 +16127,7 @@
         <v>Congenital Abnormality</v>
       </c>
       <c r="H8" t="str">
-        <v>2522</v>
+        <v>2990</v>
       </c>
       <c r="I8" t="str">
         <v>editor</v>
@@ -16142,7 +16142,7 @@
         <v/>
       </c>
       <c r="M8" t="str">
-        <v>[{"expression":"$AdmReason = 'NTD'","name":"Admitted with NTD","type":"sign","weight":"1.0","position":1,"symptomId":"8259e084-e803-4668-afa6-5034e77efb1a","printable":true,"keyId":"486c28a5-d2fd-4b57-a8d2-5d0ac85ee069"},{"expression":"$AdmReason = 'Cong'","name":"Admitted with other congenital abnormality","type":"sign","weight":"1.0","position":2,"symptomId":"10b025aa-7cf0-45a6-9ef7-ece0805132ce","printable":true,"keyId":"75ab39e6-aab2-47fa-a910-b837ab7a6970"},{"expression":"$Spine = 'NTD'","name":"Spinal NTD","type":"sign","weight":"1.0","position":3,"symptomId":"b6b4fb5f-e97c-4868-8d6d-3ebab4c37d56","printable":true,"keyId":"d4088f18-260b-4f7b-b539-c842e5cc6967"},{"expression":"$Abdomen = 'Defect'","name":"Abdominal wall defect","type":"sign","weight":"1.0","position":4,"symptomId":"584fae7d-31bf-4c75-bd1a-775a3b9a28b7","printable":true,"keyId":"a62b4197-0057-4aef-9552-c708d217b3fb"},{"expression":"$Umbilicus = 'Abn'","name":"Abnormal umbilicus","type":"sign","weight":"1.0","position":5,"symptomId":"174f33ed-5221-4a0e-9092-dd5adc90f2cf","printable":true,"keyId":"0966c65b-a895-4f04-a483-0d1c11f7c0e4"},{"expression":"$Anus = 'Imp'","name":"Imperforate anus","type":"sign","weight":"1.0","position":6,"symptomId":"3e633fd9-54ad-4300-86c8-67af9442c87c","printable":true,"keyId":"196f4a7f-1604-4a17-8fe5-fd33842ac47b"},{"expression":"$MSKproblems = 'MSKD'","name":"Musculoskeletal deformity e.g. talipes ","type":"sign","weight":"1.0","position":7,"symptomId":"7dc59298-d5bc-450d-a43c-7871ebc0395b","printable":true,"keyId":"f6ea0870-52c9-4514-9f77-871ce3febea1"},{"expression":"$HeadShape = 'Hydro'","name":"Head Shape","type":"sign","weight":"1.0","position":8,"symptomId":"5fc63e30-577e-48b8-9872-e7a15a24b0f1","printable":true,"keyId":"d59a969e-75ad-476d-ba12-582e13ffa29b"}]</v>
+        <v>[{"expression":"$AdmReason = 'NTD'","name":"Admitted with NTD","type":"sign","weight":"1.0","position":1,"symptomId":"8259e084-e803-4668-afa6-5034e77efb1a","printable":true,"keyId":"486c28a5-d2fd-4b57-a8d2-5d0ac85ee069","key":"Admitted with NTD"},{"expression":"$AdmReason = 'Cong'","name":"Admitted with other congenital abnormality","type":"sign","weight":"1.0","position":2,"symptomId":"10b025aa-7cf0-45a6-9ef7-ece0805132ce","printable":true,"keyId":"75ab39e6-aab2-47fa-a910-b837ab7a6970","key":"Admitted with other congenital abnormality"},{"expression":"$Spine = 'NTD'","name":"Spinal NTD","type":"sign","weight":"1.0","position":3,"symptomId":"b6b4fb5f-e97c-4868-8d6d-3ebab4c37d56","printable":true,"keyId":"d4088f18-260b-4f7b-b539-c842e5cc6967","key":"Spinal NTD"},{"expression":"$Abdomen = 'Defect'","name":"Abdominal wall defect","type":"sign","weight":"1.0","position":4,"symptomId":"584fae7d-31bf-4c75-bd1a-775a3b9a28b7","printable":true,"keyId":"a62b4197-0057-4aef-9552-c708d217b3fb","key":"Abdominal wall defect"},{"expression":"$Umbilicus = 'Abn'","name":"Abnormal umbilicus","type":"sign","weight":"1.0","position":5,"symptomId":"174f33ed-5221-4a0e-9092-dd5adc90f2cf","printable":true,"keyId":"0966c65b-a895-4f04-a483-0d1c11f7c0e4","key":"Abnormal umbilicus"},{"expression":"$Anus = 'Imp'","name":"Imperforate anus","type":"sign","weight":"1.0","position":6,"symptomId":"3e633fd9-54ad-4300-86c8-67af9442c87c","printable":true,"keyId":"196f4a7f-1604-4a17-8fe5-fd33842ac47b","key":"Imperforate anus"},{"expression":"$MSKproblems = 'MSKD'","name":"Musculoskeletal deformity e.g. talipes","type":"sign","weight":"1.0","position":7,"symptomId":"7dc59298-d5bc-450d-a43c-7871ebc0395b","printable":true,"keyId":"f6ea0870-52c9-4514-9f77-871ce3febea1","key":"Musculoskeletal deformity e.g. talipes"},{"expression":"$HeadShape = 'Hydro'","name":"Head Shape","type":"sign","weight":"1.0","position":8,"symptomId":"5fc63e30-577e-48b8-9872-e7a15a24b0f1","printable":true,"keyId":"d59a969e-75ad-476d-ba12-582e13ffa29b","key":"Head Shape"}]</v>
       </c>
       <c r="N8" t="str" xml:space="preserve">
         <v xml:space="preserve">Congenital abnormality Includes:
@@ -16213,7 +16213,7 @@
         <v>Pneumonia / Bronchiolitis</v>
       </c>
       <c r="H9" t="str">
-        <v>2523</v>
+        <v>2991</v>
       </c>
       <c r="I9" t="str">
         <v>editor</v>
@@ -16228,7 +16228,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"a7ecb10c-8957-4ed7-97bd-71e79c5720a3","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183"},{"expression":"$RR &gt; 80","name":"Tachypnoea &gt; 80","type":"sign","weight":"1.0","position":2,"symptomId":"e9c10413-b86a-4da9-a9cd-572d46cd0dd5","printable":true,"keyId":"12de2633-b99b-448d-97f8-dadd21f5b8a8"},{"expression":"$RespSR = 'DIB'","name":"History of Fast or laboured breathing","type":"sign","weight":"1.0","position":3,"symptomId":"969789fe-4756-4eb8-86c8-fea478291c43","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f"},{"expression":"$RespSR = 'NBr'","name":"History of Noisy breathing","type":"sign","weight":"1.0","position":4,"symptomId":"5d8b9512-af53-44fa-b36d-d457f5f2a335","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904"},{"expression":"$RespSR = 'Cough'","name":"History of cough","type":"sign","weight":"1.0","position":5,"symptomId":"c6ea7dba-70b3-4151-8285-a295780c911c","printable":true,"keyId":"caed4149-c7fb-414d-9878-a55142ee5c26"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of WOB","type":"sign","weight":"1.0","position":6,"symptomId":"b6f1fb35-40c7-40e3-b5cc-858b8e946d62","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb"},{"expression":"$SatsAir &lt; 90","name":"Sats in air &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"38526453-d71c-4f3f-926a-415cad8dc532","printable":true,"keyId":"6d33d3b7-4ea1-45b8-a724-365ac781b54a"},{"expression":"$SatsO2 &lt; 90","name":"Sats in oxygen &lt; 90","type":"sign","weight":"1.0","position":8,"symptomId":"a0192530-9b4b-4176-9da3-b12b5e84c0ab","printable":true,"keyId":"f3e96fd9-4195-41a1-92f3-e4e9e0f171b0"},{"expression":"$ChestAusc = 'BilatCr' or $ChestAusc = 'UniCr' or $ChestAusc = 'UniWh'","name":"Any chest signs","type":"sign","weight":"1.0","position":9,"symptomId":"1db6a7ca-31ea-4029-9fcb-e9a3cbc63bad","printable":true,"keyId":"dab77bf4-8e4c-4019-a9ca-2de7844688f4"}]</v>
+        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"a7ecb10c-8957-4ed7-97bd-71e79c5720a3","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183","key":"Grunting or severe recessions"},{"expression":"$RR &gt; 80","name":"Tachypnoea &gt; 80","type":"sign","weight":"1.0","position":2,"symptomId":"e9c10413-b86a-4da9-a9cd-572d46cd0dd5","printable":true,"keyId":"12de2633-b99b-448d-97f8-dadd21f5b8a8","key":"Tachypnoea &gt; 80"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":3,"symptomId":"969789fe-4756-4eb8-86c8-fea478291c43","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f","key":"History of fast or laboured breathing"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":4,"symptomId":"5d8b9512-af53-44fa-b36d-d457f5f2a335","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904","key":"History of noisy breathing"},{"expression":"$RespSR = 'Cough'","name":"History of cough","type":"sign","weight":"1.0","position":5,"symptomId":"c6ea7dba-70b3-4151-8285-a295780c911c","printable":true,"keyId":"caed4149-c7fb-414d-9878-a55142ee5c26","key":"History of cough"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of WOB","type":"sign","weight":"1.0","position":6,"symptomId":"b6f1fb35-40c7-40e3-b5cc-858b8e946d62","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb","key":"Any severity of WOB"},{"expression":"$SatsAir &lt; 90","name":"Sats in air &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"38526453-d71c-4f3f-926a-415cad8dc532","printable":true,"keyId":"6d33d3b7-4ea1-45b8-a724-365ac781b54a","key":"Sats in air &lt; 90"},{"expression":"$SatsO2 &lt; 90","name":"Sats in oxygen &lt; 90","type":"sign","weight":"1.0","position":8,"symptomId":"a0192530-9b4b-4176-9da3-b12b5e84c0ab","printable":true,"keyId":"f3e96fd9-4195-41a1-92f3-e4e9e0f171b0","key":"Sats in oxygen &lt; 90"},{"expression":"$ChestAusc = 'BilatCr' or $ChestAusc = 'UniCr' or $ChestAusc = 'UniWh'","name":"Any chest signs","type":"sign","weight":"1.0","position":9,"symptomId":"1db6a7ca-31ea-4029-9fcb-e9a3cbc63bad","printable":true,"keyId":"dab77bf4-8e4c-4019-a9ca-2de7844688f4","key":"Any chest signs"}]</v>
       </c>
       <c r="N9" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Airway and respiratory support
@@ -16298,7 +16298,7 @@
         <v>Transient Tachypnoea of Newborn (TTN)</v>
       </c>
       <c r="H10" t="str">
-        <v>2524</v>
+        <v>2992</v>
       </c>
       <c r="I10" t="str">
         <v>editor</v>
@@ -16313,7 +16313,7 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"5dd776f0-1ba6-4be7-9999-53d35ba0b348","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":2,"symptomId":"152d0589-d3bb-4d6b-8a9c-f73dee348a5b","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f"},{"expression":"$RespSR = 'NBr'","name":"History of Noisy breathing","type":"sign","weight":"1.0","position":3,"symptomId":"d7394fee-0bad-4692-a512-4ce3149de8ab","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any Severity of WOB","type":"sign","weight":"1.0","position":4,"symptomId":"54fd05e3-1bc1-4749-89a7-d1775a56f6e1","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb"},{"expression":"$SatsAir &lt; 90","name":"Saturations in Air &lt; 90","type":"sign","weight":"1.0","position":5,"symptomId":"ad716402-b9a4-49bf-876c-d95dcae7897e","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in O2 &lt; 90","type":"sign","weight":"1.0","position":6,"symptomId":"e6b10a8c-6a2a-4104-b743-4a6290060da6","printable":true,"keyId":"788d5f77-bd1b-4587-b464-dd1cac7832b6"},{"expression":"$Temperature &gt; 37.4","name":"Fever","type":"sign","weight":"1.0","position":7,"symptomId":"f8805c22-b82e-4746-9ce1-916705a8972c","printable":true,"keyId":"2ac6973c-b41a-4773-b116-7f3c3c6972bc"},{"expression":"$AdmReason = 'Fev'","name":"Admitted with fever","type":"sign","weight":"1.0","position":8,"symptomId":"8108084c-90be-496e-9e8d-8c7a9c7b8c2e","printable":true,"keyId":"236d35cc-e199-40bc-9268-7787544c3e64"},{"expression":"$SRNeuroOther = 'F'","name":"History of fever","type":"sign","weight":"1.0","position":9,"symptomId":"6d76565d-3f5f-42ce-82e6-f8c85542ca5c","printable":true,"keyId":"ec62779b-c482-4365-a07a-d8c2092c975c"},{"expression":"$Skin = 'PUST'","name":"Pustules all over body","type":"sign","weight":"1.0","position":10,"symptomId":"00a80f39-8bfd-409b-9d22-ec8fefddb7c7","printable":true,"keyId":"e1144e0a-3459-4109-8e9b-feaabb85bc3a"},{"expression":"$Skin = 'BOIL'","name":"Big Boil","type":"sign","weight":"1.0","position":11,"symptomId":"981daa8a-938a-4f4a-9a4b-84696164828e","printable":true,"keyId":"d9226b55-5b85-4363-bb16-52a31c21a1c3"},{"expression":"$Umbilicus = 'Inf'","name":"Infected umbilicus","type":"sign","weight":"1.0","position":12,"symptomId":"722387b9-d414-4d10-895e-73835563526d","printable":true,"keyId":"568e168d-3fd4-4ad5-ad4b-f774bbc4569f"},{"expression":"$Fontanelle = 'Bulg'","name":"Bulging fontanelle","type":"sign","weight":"1.0","position":13,"symptomId":"69aadd9b-319a-4c58-bb71-407dba9be0f5","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d"},{"expression":"$RespSR = 'Apn'","name":"History of Apnoea","type":"sign","weight":"1.0","position":14,"symptomId":"aa431dca-cf7e-4046-b685-19e1b0a9c35b","printable":true,"keyId":"9e18e7fc-f134-41af-aa5a-faf95d633c7f"},{"expression":"$Colour = 'White'","name":"Pallor","type":"sign","weight":"0.5","position":15,"symptomId":"87912150-bf54-4c2e-b68b-87be3a04c032","printable":true,"keyId":"b00e7d87-6725-4bbf-9fd1-712e35fb7f30"},{"expression":"$Activity = 'Leth'","name":"Lethargy","type":"sign","weight":"1.0","position":16,"symptomId":"a0a3ab95-776c-4a5e-aba3-ae914aa3767b","printable":true,"keyId":"7e0ba1d1-acac-4d00-8dd4-457d6a004749"},{"expression":"$Activity = 'Irrit'","name":"Irritability","type":"sign","weight":"0.5","position":17,"symptomId":"2f74a1d7-79ee-4767-a84f-1d4754cee4dd","printable":true,"keyId":"be8220ad-ade4-41c7-bff0-c76ce63d94d3"},{"expression":"($HR &gt; 159 and $Temperature &lt; 37.5) or ($HR &gt; 159 and $BabyCryTriage = true)","name":"Tachy without fever or crying","type":"sign","weight":"0.5","position":18,"symptomId":"2447169d-68b1-45cb-afea-adbed63125a1","printable":true,"keyId":"414d03e1-ee16-411a-8750-3151c79e8437"},{"expression":"$HRManual &gt; 159 and $Temperature &lt; 37.5","name":"Manual tachy without fever","type":"sign","weight":"0.5","position":19,"symptomId":"44e257a6-f41e-42df-9481-d2c275576607","printable":true,"keyId":"e5203db6-0bf6-45fe-bf0e-dae78ffc0871"},{"expression":"$Colour = 'Yell'","name":"Jaundice (&lt;24hrs)","type":"sign","weight":"1.0","position":20,"symptomId":"6024be3c-5b2f-4822-91ed-2e5a50e9ebf2","printable":true,"keyId":"c5acddf2-6265-4f66-a18f-5559a66bc5b2"},{"expression":"$SuckReflex = 'Weak' or $SuckReflex = 'Absent'","name":"weak or absent suck","type":"sign","weight":"0.5","position":21,"symptomId":"2be2ce14-08aa-4cf9-a5f2-7557586a7490","printable":true,"keyId":"f546cef9-888b-450e-8950-640d8f870a75"},{"expression":"$Abdomen = 'Dist'","name":"Distended abdomen","type":"sign","weight":"0.5","position":22,"symptomId":"dd1dc215-c9f4-4896-a0c3-0e676065ecd0","printable":true,"keyId":"3b8cb379-ec7b-49b1-833c-8bbb8e525125"},{"expression":"$RFSepsis = 'MF' or $RFSepsis = 'OL' or $RFSepsis = 'PROM' or $RFSepsis = 'Pr2nd'","name":"Any full risk factor for sepsis","type":"risk","weight":"1.0","position":23,"symptomId":"c6a0bd6e-d2b5-4b9b-939d-50ee1f2247ff","printable":true,"keyId":"8ca256c9-770f-4863-b753-aedd6a3edb5e"},{"expression":"$RFSepsis = 'BBA'","name":"Born before arrival","type":"risk","weight":"0.5","position":24,"symptomId":"e0389cc6-11b8-45bf-9edc-cd5a9df4af25","printable":true,"keyId":"34f53d47-f48f-4f33-a23e-dba8ae101ca1"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":25,"symptomId":"bab820b0-5721-4995-a713-3b9e8559eb7e","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22"},{"expression":"$Vomiting = 'YesGr'","name":"Bilious vomiting","type":"sign","weight":"1.0","position":26,"symptomId":"154f938d-8411-4fd0-a7f5-90732f004dbd","printable":true,"keyId":"321ed112-b2f1-4c96-a74e-e5e4217b5bd5"},{"expression":"$FeedingReview = 'NG' or $FeedingReview = 'IVF' or $Vomiting = 'Yes' or $Vomiting = 'YesBl'","name":"Poor feeding or vomiting","type":"sign","weight":"0.5","position":27,"symptomId":"d04e2d65-ff87-40a5-aca0-5334d303d31c","printable":true,"keyId":"9537e9bc-5f14-4d9d-83c2-51302c07c8fb"}]</v>
+        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"5dd776f0-1ba6-4be7-9999-53d35ba0b348","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183","key":"Grunting or severe recessions"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":2,"symptomId":"152d0589-d3bb-4d6b-8a9c-f73dee348a5b","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f","key":"History of fast or laboured breathing"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":3,"symptomId":"d7394fee-0bad-4692-a512-4ce3149de8ab","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904","key":"History of noisy breathing"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of WOB","type":"sign","weight":"1.0","position":4,"symptomId":"54fd05e3-1bc1-4749-89a7-d1775a56f6e1","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb","key":"Any severity of WOB"},{"expression":"$SatsAir &lt; 90","name":"Saturations in air &lt; 90","type":"sign","weight":"1.0","position":5,"symptomId":"ad716402-b9a4-49bf-876c-d95dcae7897e","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2","key":"Saturations in air &lt; 90"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in O2 &lt; 90","type":"sign","weight":"1.0","position":6,"symptomId":"e6b10a8c-6a2a-4104-b743-4a6290060da6","printable":true,"keyId":"788d5f77-bd1b-4587-b464-dd1cac7832b6","key":"Saturations in O2 &lt; 90"},{"expression":"$Temperature &gt; 37.4","name":"Fever","type":"sign","weight":"1.0","position":7,"symptomId":"f8805c22-b82e-4746-9ce1-916705a8972c","printable":true,"keyId":"2ac6973c-b41a-4773-b116-7f3c3c6972bc","key":"Fever"},{"expression":"$AdmReason = 'Fev'","name":"Admitted with fever","type":"sign","weight":"1.0","position":8,"symptomId":"8108084c-90be-496e-9e8d-8c7a9c7b8c2e","printable":true,"keyId":"236d35cc-e199-40bc-9268-7787544c3e64","key":"Admitted with fever"},{"expression":"$SRNeuroOther = 'F'","name":"History of fever","type":"sign","weight":"1.0","position":9,"symptomId":"6d76565d-3f5f-42ce-82e6-f8c85542ca5c","printable":true,"keyId":"ec62779b-c482-4365-a07a-d8c2092c975c","key":"History of fever"},{"expression":"$Skin = 'PUST'","name":"Pustules all over body","type":"sign","weight":"1.0","position":10,"symptomId":"00a80f39-8bfd-409b-9d22-ec8fefddb7c7","printable":true,"keyId":"e1144e0a-3459-4109-8e9b-feaabb85bc3a","key":"Pustules all over body"},{"expression":"$Skin = 'BOIL'","name":"Big Boil","type":"sign","weight":"1.0","position":11,"symptomId":"981daa8a-938a-4f4a-9a4b-84696164828e","printable":true,"keyId":"d9226b55-5b85-4363-bb16-52a31c21a1c3","key":"Big Boil"},{"expression":"$Umbilicus = 'Inf'","name":"Infected umbilicus","type":"sign","weight":"1.0","position":12,"symptomId":"722387b9-d414-4d10-895e-73835563526d","printable":true,"keyId":"568e168d-3fd4-4ad5-ad4b-f774bbc4569f","key":"Infected umbilicus"},{"expression":"$Fontanelle = 'Bulg'","name":"Bulging fontanelle","type":"sign","weight":"1.0","position":13,"symptomId":"69aadd9b-319a-4c58-bb71-407dba9be0f5","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d","key":"Bulging fontanelle"},{"expression":"$RespSR = 'Apn'","name":"History of Apnoea","type":"sign","weight":"1.0","position":14,"symptomId":"aa431dca-cf7e-4046-b685-19e1b0a9c35b","printable":true,"keyId":"9e18e7fc-f134-41af-aa5a-faf95d633c7f","key":"History of Apnoea"},{"expression":"$Colour = 'White'","name":"Pallor","type":"sign","weight":"0.5","position":15,"symptomId":"87912150-bf54-4c2e-b68b-87be3a04c032","printable":true,"keyId":"b00e7d87-6725-4bbf-9fd1-712e35fb7f30","key":"Pallor"},{"expression":"$Activity = 'Leth'","name":"Lethargy","type":"sign","weight":"1.0","position":16,"symptomId":"a0a3ab95-776c-4a5e-aba3-ae914aa3767b","printable":true,"keyId":"7e0ba1d1-acac-4d00-8dd4-457d6a004749","key":"Lethargy"},{"expression":"$Activity = 'Irrit'","name":"Irritability","type":"sign","weight":"0.5","position":17,"symptomId":"2f74a1d7-79ee-4767-a84f-1d4754cee4dd","printable":true,"keyId":"be8220ad-ade4-41c7-bff0-c76ce63d94d3","key":"Irritability"},{"expression":"($HR &gt; 159 and $Temperature &lt; 37.5) or ($HR &gt; 159 and $BabyCryTriage = true)","name":"Tachy without fever or crying","type":"sign","weight":"0.5","position":18,"symptomId":"2447169d-68b1-45cb-afea-adbed63125a1","printable":true,"keyId":"414d03e1-ee16-411a-8750-3151c79e8437","key":"Tachy without fever or crying"},{"expression":"$HRManual &gt; 159 and $Temperature &lt; 37.5","name":"Manual tachy without fever","type":"sign","weight":"0.5","position":19,"symptomId":"44e257a6-f41e-42df-9481-d2c275576607","printable":true,"keyId":"e5203db6-0bf6-45fe-bf0e-dae78ffc0871","key":"Manual tachy without fever"},{"expression":"$Colour = 'Yell'","name":"Jaundice (&lt;24hrs)","type":"sign","weight":"1.0","position":20,"symptomId":"6024be3c-5b2f-4822-91ed-2e5a50e9ebf2","printable":true,"keyId":"c5acddf2-6265-4f66-a18f-5559a66bc5b2","key":"Jaundice (&lt;24hrs)"},{"expression":"$SuckReflex = 'Weak' or $SuckReflex = 'Absent'","name":"weak or absent suck","type":"sign","weight":"0.5","position":21,"symptomId":"2be2ce14-08aa-4cf9-a5f2-7557586a7490","printable":true,"keyId":"f546cef9-888b-450e-8950-640d8f870a75","key":"weak or absent suck"},{"expression":"$Abdomen = 'Dist'","name":"Distended abdomen","type":"sign","weight":"0.5","position":22,"symptomId":"dd1dc215-c9f4-4896-a0c3-0e676065ecd0","printable":true,"keyId":"3b8cb379-ec7b-49b1-833c-8bbb8e525125","key":"Distended abdomen"},{"expression":"$RFSepsis = 'MF' or $RFSepsis = 'OL' or $RFSepsis = 'PROM' or $RFSepsis = 'Pr2nd'","name":"Any full risk factor for sepsis","type":"risk","weight":"1.0","position":23,"symptomId":"c6a0bd6e-d2b5-4b9b-939d-50ee1f2247ff","printable":true,"keyId":"8ca256c9-770f-4863-b753-aedd6a3edb5e","key":"Any full risk factor for sepsis"},{"expression":"$RFSepsis = 'BBA'","name":"Born before arrival","type":"risk","weight":"0.5","position":24,"symptomId":"e0389cc6-11b8-45bf-9edc-cd5a9df4af25","printable":true,"keyId":"34f53d47-f48f-4f33-a23e-dba8ae101ca1","key":"Born before arrival"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":25,"symptomId":"bab820b0-5721-4995-a713-3b9e8559eb7e","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22","key":"Convulsions"},{"expression":"$Vomiting = 'YesGr'","name":"Bilious vomiting","type":"sign","weight":"1.0","position":26,"symptomId":"154f938d-8411-4fd0-a7f5-90732f004dbd","printable":true,"keyId":"321ed112-b2f1-4c96-a74e-e5e4217b5bd5","key":"Bilious vomiting"},{"expression":"$FeedingReview = 'NG' or $FeedingReview = 'IVF' or $Vomiting = 'Yes' or $Vomiting = 'YesBl'","name":"Poor feeding or vomiting","type":"sign","weight":"0.5","position":27,"symptomId":"d04e2d65-ff87-40a5-aca0-5334d303d31c","printable":true,"keyId":"9537e9bc-5f14-4d9d-83c2-51302c07c8fb","key":"Poor feeding or vomiting"}]</v>
       </c>
       <c r="N10" t="str" xml:space="preserve">
         <v xml:space="preserve">These babies are not unwell 
@@ -16384,7 +16384,7 @@
         <v>Umbilical Hernia</v>
       </c>
       <c r="H11" t="str">
-        <v>2525</v>
+        <v>2993</v>
       </c>
       <c r="I11" t="str">
         <v>editor</v>
@@ -16461,7 +16461,7 @@
         <v>Meningitis</v>
       </c>
       <c r="H12" t="str">
-        <v>2526</v>
+        <v>2994</v>
       </c>
       <c r="I12" t="str">
         <v>editor</v>
@@ -16476,7 +16476,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>[{"expression":"$Fontanelle = 'Bulg'","name":"Bulging fontanelle","type":"sign","weight":"1.0","position":1,"symptomId":"634790a2-39ba-4dc9-9acc-91f11895738e","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d"},{"expression":"$Tone = 'High'","name":"Increased tone","type":"sign","weight":"1.0","position":2,"symptomId":"446df1b1-f856-49e7-9462-cef4073b9a7e","printable":true,"keyId":"152d0a63-6627-405e-a091-1bcccd0fc319"},{"expression":"$Activity = 'Irrit'","name":"Activity irritable","type":"sign","weight":"0.5","position":3,"symptomId":"1c28bf25-41fd-465f-b699-b2fa9da0295c","printable":true,"keyId":"f37de1b4-0ef0-4a1e-ae55-8407a3ef54e3"},{"expression":"$Activity = 'Leth'","name":"Activity Lethargic","type":"sign","weight":"0.5","position":4,"symptomId":"2520a591-1d3e-47c2-833d-ce2168c93291","printable":true,"keyId":"c77857fa-2dcf-4ef9-8b82-d05118424611"}]</v>
+        <v>[{"expression":"$Fontanelle = 'Bulg'","name":"Bulging fontanelle","type":"sign","weight":"1.0","position":1,"symptomId":"634790a2-39ba-4dc9-9acc-91f11895738e","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d","key":"Bulging fontanelle"},{"expression":"$Tone = 'High'","name":"Increased tone","type":"sign","weight":"1.0","position":2,"symptomId":"446df1b1-f856-49e7-9462-cef4073b9a7e","printable":true,"keyId":"152d0a63-6627-405e-a091-1bcccd0fc319","key":"Increased tone"},{"expression":"$Activity = 'Irrit'","name":"Activity irritable","type":"sign","weight":"0.5","position":3,"symptomId":"1c28bf25-41fd-465f-b699-b2fa9da0295c","printable":true,"keyId":"f37de1b4-0ef0-4a1e-ae55-8407a3ef54e3","key":"Activity irritable"},{"expression":"$Activity = 'Leth'","name":"Activity Lethargic","type":"sign","weight":"0.5","position":4,"symptomId":"2520a591-1d3e-47c2-833d-ce2168c93291","printable":true,"keyId":"c77857fa-2dcf-4ef9-8b82-d05118424611","key":"Activity Lethargic"}]</v>
       </c>
       <c r="N12" t="str">
         <v>Clinical instructions to be added here</v>
@@ -16538,7 +16538,7 @@
         <v>Ambiguous Genetalia</v>
       </c>
       <c r="H13" t="str">
-        <v>2527</v>
+        <v>2995</v>
       </c>
       <c r="I13" t="str">
         <v>editor</v>
@@ -16615,7 +16615,7 @@
         <v>Untreated Maternal Syphilis</v>
       </c>
       <c r="H14" t="str">
-        <v>2528</v>
+        <v>2996</v>
       </c>
       <c r="I14" t="str">
         <v>editor</v>
@@ -16692,7 +16692,7 @@
         <v>Abdominal obstruction</v>
       </c>
       <c r="H15" t="str">
-        <v>2529</v>
+        <v>2997</v>
       </c>
       <c r="I15" t="str">
         <v>editor</v>
@@ -16707,7 +16707,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>[{"expression":"$PassedMec = 'NoMec'","name":"Not Passed Meconium in 1st 24 hrs","type":"sign","weight":"1.0","position":1,"symptomId":"3f975a00-345e-4dd5-90fa-da4072d664e8","printable":true,"keyId":"0c7367cb-1e09-4a44-b46f-2896adb20558"},{"expression":"$Vomiting = 'Yes'","name":"Vomiting all feeds","type":"sign","weight":"1.0","position":2,"symptomId":"55de2cd8-ca96-40dc-af30-1a90ba6904cc","printable":true,"keyId":"3de031ad-8481-4065-865b-187136d726f9"},{"expression":"$Vomiting = 'YesBl'","name":"Vomiting with blood","type":"sign","weight":"1.0","position":3,"symptomId":"bd19036b-5121-4a8f-9b46-6072cf77d446","printable":true,"keyId":"4093f805-412c-4b55-992b-bde11ddd12d9"},{"expression":"$StoolsInfant = 'BNO'","name":"Bowels not open","type":"sign","weight":"1.0","position":4,"symptomId":"5ab0a049-3979-47f8-bdf9-7fec55427aa1","printable":true,"keyId":"7dca9ab0-34e8-4e3c-bb7f-1c0355e8b616"},{"expression":"$Abdomen = 'Dist'","name":"Abdominal distension","type":"sign","weight":"1.0","position":5,"symptomId":"2d8e0374-4950-4cfe-b511-7c10cba9cd0e","printable":true,"keyId":"1d130ae2-9cfa-4370-972b-c0b563dfb87c"}]</v>
+        <v>[{"expression":"$PassedMec = 'NoMec'","name":"Not Passed Meconium in 1st 24 hrs","type":"sign","weight":"1.0","position":1,"symptomId":"3f975a00-345e-4dd5-90fa-da4072d664e8","printable":true,"keyId":"0c7367cb-1e09-4a44-b46f-2896adb20558","key":"Not Passed Meconium in 1st 24 hrs"},{"expression":"$Vomiting = 'Yes'","name":"Vomiting all feeds","type":"sign","weight":"1.0","position":2,"symptomId":"55de2cd8-ca96-40dc-af30-1a90ba6904cc","printable":true,"keyId":"3de031ad-8481-4065-865b-187136d726f9","key":"Vomiting all feeds"},{"expression":"$Vomiting = 'YesBl'","name":"Vomiting with blood","type":"sign","weight":"1.0","position":3,"symptomId":"bd19036b-5121-4a8f-9b46-6072cf77d446","printable":true,"keyId":"4093f805-412c-4b55-992b-bde11ddd12d9","key":"Vomiting with blood"},{"expression":"$StoolsInfant = 'BNO'","name":"Bowels not open","type":"sign","weight":"1.0","position":4,"symptomId":"5ab0a049-3979-47f8-bdf9-7fec55427aa1","printable":true,"keyId":"7dca9ab0-34e8-4e3c-bb7f-1c0355e8b616","key":"Bowels not open"},{"expression":"$Abdomen = 'Dist'","name":"Abdominal distension","type":"sign","weight":"1.0","position":5,"symptomId":"2d8e0374-4950-4cfe-b511-7c10cba9cd0e","printable":true,"keyId":"1d130ae2-9cfa-4370-972b-c0b563dfb87c","key":"Abdominal distension"}]</v>
       </c>
       <c r="N15" t="str">
         <v>Clinical instructions to be added here</v>
@@ -16769,7 +16769,7 @@
         <v>Risk factors for sepsis (Not symptomatic)</v>
       </c>
       <c r="H16" t="str">
-        <v>2530</v>
+        <v>2998</v>
       </c>
       <c r="I16" t="str">
         <v>editor</v>
@@ -16784,7 +16784,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>[{"expression":"$RFSepsis = 'MF'","name":"Maternal Fever in Labour","type":"risk","weight":"1.0","position":1,"symptomId":"377f5ff2-d304-462a-a511-ad8bbbe68aa9","printable":true,"keyId":"6531353e-d6c8-4dba-aca2-9d7b46f7c83b"},{"expression":"$RFSepsis = 'OL'","name":"Offensive Liquor","type":"risk","weight":"1.0","position":2,"symptomId":"339975d7-dbf5-4ce6-9fce-d13ced1b22a2","printable":true,"keyId":"e6da16c9-4d4b-42b0-b2d8-f1a165887bee"},{"expression":"$RFSepsis = 'PROM'","name":"PROM &gt; 18 hrs","type":"risk","weight":"1.0","position":3,"symptomId":"7d1d6acc-f759-4dd6-8e87-d3fd9d6f4ef8","printable":true,"keyId":"d50c463e-2dbe-4f87-8a01-c75f4f62d16d"},{"expression":"$Temperature &gt; 37.4","name":"Temp &gt; 37.4","type":"sign","weight":"1.0","position":4,"symptomId":"d4a71de1-6afc-45c2-b3ba-7c62a8035465","printable":true,"keyId":"6a945f1f-ba0f-4718-8285-fd90e4a49ab3"},{"expression":"$Skin = 'PUST'","name":"Pustules all over body","type":"sign","weight":"1.0","position":5,"symptomId":"da295ad5-3794-400d-b8d8-444130fd2751","printable":true,"keyId":"e1144e0a-3459-4109-8e9b-feaabb85bc3a"},{"expression":"$Skin = 'BOIL'","name":"Big Boil","type":"sign","weight":"1.0","position":6,"symptomId":"929ca60e-61ec-47bb-8726-c52f14ecfab3","printable":true,"keyId":"d9226b55-5b85-4363-bb16-52a31c21a1c3"},{"expression":"$Umbilicus = 'Inf'","name":"Infected umbilicus","type":"sign","weight":"1.0","position":7,"symptomId":"682966dd-4c19-4ab1-aa15-7b1921f01310","printable":true,"keyId":"568e168d-3fd4-4ad5-ad4b-f774bbc4569f"},{"expression":"$Fontanelle = 'Bulg'","name":"Bulging Fontanelle","type":"sign","weight":"1.0","position":8,"symptomId":"68323f23-4a79-42ad-9909-fefc64460460","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d"},{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":9,"symptomId":"298989ba-06ad-45ad-ad3f-b58470df5913","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183"},{"expression":"$RespSR = 'Apn'","name":"Apneoa","type":"sign","weight":"1.0","position":10,"symptomId":"45c626fe-0083-4f8e-b57d-9e9126c1e740","printable":true,"keyId":"22f4f401-0541-4994-ad5c-22f2a9a659e1"},{"expression":"$WOBSev = 'Sev'","name":"Severe WOB","type":"sign","weight":"1.0","position":11,"symptomId":"13a1854e-15a9-4a81-aca5-e6ca839c938b","printable":true,"keyId":"28ba5996-b2f2-4709-97f7-07246e2df9f4"},{"expression":"$WOBSev = 'Mod'","name":"Moderate WOB","type":"sign","weight":"1.0","position":12,"symptomId":"7af212a6-903a-4317-bbc3-150616980ff0","printable":true,"keyId":"d63ec530-2e03-41f0-82ca-9d078732734b"},{"expression":"$AdmReason = 'Fev'","name":"Reason for admission - Fever","type":"sign","weight":"1.0","position":13,"symptomId":"8c74d86d-fe80-4734-a8a5-86ba59059804","printable":true,"keyId":"c6df56b0-2574-48c9-9866-ce02831969dd"},{"expression":"$SRNeuroOther = 'F'","name":"Other symptoms - Fever","type":"sign","weight":"1.0","position":14,"symptomId":"fea993f2-d228-4f00-8425-827fd5f99a9c","printable":true,"keyId":"029e7ca2-2aa9-4600-9aee-b22a5aecf0da"},{"expression":"$RR &gt; 59 and ($AgeCat = 'NB24' or $AgeCat = 'NB48' or $AgeCat = 'INF72')","name":"Tachypnoea &gt; 59 in all ages except &lt; 2hrs old","type":"sign","weight":"1.0","position":15,"symptomId":"8b47901b-cabf-4a02-8891-5f92856fbd59","printable":true,"keyId":"14ba42cb-bc23-4d31-ae51-3f4a756c4701"},{"expression":"$Activity = 'Leth'","name":"Lethargic","type":"sign","weight":"1.0","position":16,"symptomId":"9289a7e1-1f30-42e5-88ff-4dced3fb7645","printable":true,"keyId":"5068af13-76b7-4a76-988d-4dabc945f304"},{"expression":"$WOBSev = 'Mild'","name":"Mild WOB","type":"sign","weight":"0.5","position":17,"symptomId":"40c85580-e33b-428e-b7a7-767f308c0b5f","printable":true,"keyId":"31fef7a4-01fb-411e-8200-ed20bec16a3a"},{"expression":"($HR &gt; 159 and $Temperature &lt; 37.5) or ($HR &gt; 159 and $BabyCryTriage = true)","name":"Tachycardia without fever or crying","type":"sign","weight":"0.5","position":18,"symptomId":"5601f609-3b5a-497c-9674-4fb27b167abb","printable":true,"keyId":"0c50f955-57f7-48cb-9455-22ea5f23c72e"},{"expression":"$HRManual &gt; 159 and $Temperature &lt; 37.5","name":"Manual Tachy without fever","type":"sign","weight":"0.5","position":19,"symptomId":"f5ad7207-caf6-4a4d-9cdb-d014ca73a123","printable":true,"keyId":"e5203db6-0bf6-45fe-bf0e-dae78ffc0871"},{"expression":"$Colour = 'White'","name":"Pallor","type":"sign","weight":"0.5","position":20,"symptomId":"ca4679d6-906d-4c3d-b242-afd835a752ba","printable":true,"keyId":"b00e7d87-6725-4bbf-9fd1-712e35fb7f30"},{"expression":"$FeedingReview = 'NG' or $FeedingReview = 'IVF' or $Vomiting = 'Yes' or $Vomiting = 'YesBl'","name":"Poor feeding","type":"sign","weight":"0.5","position":21,"symptomId":"9d4f2151-3747-4b98-8023-5a5c1802f076","printable":true,"keyId":"94c3d0f7-71af-4069-bf59-2db364eedf7f"},{"expression":"($SuckReflex = 'Weak' or $SuckReflex = 'Absent') and $Gestation &gt; 33","name":"Weak Suck &amp; Gestation &gt; 33 weeks","type":"sign","weight":"0.5","position":22,"symptomId":"069b331a-12f2-4986-9e1e-4a147199c043","printable":true,"keyId":"97c07758-0787-4b02-9f3a-5a7a7d6f55b6"},{"expression":"$Activity = 'Irrit'","name":"Irritable","type":"sign","weight":"0.5","position":23,"symptomId":"5aeb3513-6fb6-408c-ba9c-cb68fb97f851","printable":true,"keyId":"55d2ba10-8cad-4618-a57b-211a2f5e64f4"},{"expression":"$RFSepsis = 'Pr2nd'","name":"Prolonged 2nd stage","type":"risk","weight":"1.0","position":24,"symptomId":"ff76a8e3-0e99-4758-b1d0-b1c263b931e1","printable":true,"keyId":"3c53da79-b51b-4c07-a0ee-d90172eadc5c"},{"expression":"$RFSepsis = 'BBA'","name":"Born before arrival","type":"risk","weight":"0.5","position":25,"symptomId":"43abc519-92e8-41fe-b3e5-1d1e22a836d9","printable":true,"keyId":"34f53d47-f48f-4f33-a23e-dba8ae101ca1"},{"expression":"$Gestation &lt; 37 and $Gestation &gt; 31","name":"Prematurity 32-36","type":"risk","weight":"0.5","position":26,"symptomId":"46079fb8-5694-4845-92e5-c5a5ae4a13c0","printable":true,"keyId":"ed62f9ba-9c40-4a28-a209-e240685fe4ee"},{"expression":"$Colour = 'Yell' and ($AgeCat = 'FNB' or $AgeCat = 'NB24')","name":"Jaundice &lt; 24 hrs","type":"sign","weight":"1.0","position":27,"symptomId":"d09d7a08-5d38-4af3-a558-34f1bcf48a70","printable":true,"keyId":"c6d9c843-e1fc-4422-9ee0-d76bdc94ecd2"},{"expression":"$Gestation &lt; 32","name":"Very or extremely prem (&lt;32 wks)","type":"risk","weight":"1.0","position":28,"symptomId":"727357db-45f2-4042-ac54-76f1d9beb2c8","printable":true,"keyId":"6c849406-ad8c-4178-a278-0184363bf209"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":29,"symptomId":"27b1146c-00be-4aac-a1aa-afb03d24c877","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22"},{"expression":"$Abdomen = 'Dist'","name":"Distended Abdomen","type":"sign","weight":"0.5","position":30,"symptomId":"1478f323-98f4-4844-84a0-593d2dc8349b","printable":true,"keyId":"3b8cb379-ec7b-49b1-833c-8bbb8e525125"},{"expression":"$Vomiting = 'YesGr'","name":"Bilious vomiting","type":"sign","weight":"1.0","position":31,"symptomId":"bc295b44-ed10-4b68-8890-7e1a9be72d67","printable":true,"keyId":"321ed112-b2f1-4c96-a74e-e5e4217b5bd5"},{"expression":"$RR &gt; 80 and $AgeCat = 'FNB'","name":"RR &gt; 80 in &lt; 2 hrs","type":"sign","weight":"1.0","position":32,"symptomId":"1c54d12f-bffd-4c18-b552-ec8f33201679","printable":true,"keyId":"6a4da821-d01d-4659-88d4-c59663b0bd6e"},{"expression":"$RR &gt; 59 and $RR &lt; 81 and $AgeCat = 'FNB'","name":"RR 60-80 &lt; 2hrs ","type":"sign","weight":"0.5","position":33,"symptomId":"421565c9-6e19-42de-82ca-8f910ce4cd57","printable":true,"keyId":"871f773e-c361-4421-b95b-aefbce4b3ade"}]</v>
+        <v>[{"expression":"$RFSepsis = 'MF'","name":"Maternal Fever in Labour","type":"risk","weight":"1.0","position":1,"symptomId":"377f5ff2-d304-462a-a511-ad8bbbe68aa9","printable":true,"keyId":"6531353e-d6c8-4dba-aca2-9d7b46f7c83b","key":"Maternal Fever in Labour"},{"expression":"$RFSepsis = 'OL'","name":"Offensive Liquor","type":"risk","weight":"1.0","position":2,"symptomId":"339975d7-dbf5-4ce6-9fce-d13ced1b22a2","printable":true,"keyId":"e6da16c9-4d4b-42b0-b2d8-f1a165887bee","key":"Offensive Liquor"},{"expression":"$RFSepsis = 'PROM'","name":"PROM &gt; 18 hrs","type":"risk","weight":"1.0","position":3,"symptomId":"7d1d6acc-f759-4dd6-8e87-d3fd9d6f4ef8","printable":true,"keyId":"d50c463e-2dbe-4f87-8a01-c75f4f62d16d","key":"PROM &gt; 18 hrs"},{"expression":"$Temperature &gt; 37.4","name":"Temp &gt; 37.4","type":"sign","weight":"1.0","position":4,"symptomId":"d4a71de1-6afc-45c2-b3ba-7c62a8035465","printable":true,"keyId":"6a945f1f-ba0f-4718-8285-fd90e4a49ab3","key":"Temp &gt; 37.4"},{"expression":"$Skin = 'PUST'","name":"Pustules all over body","type":"sign","weight":"1.0","position":5,"symptomId":"da295ad5-3794-400d-b8d8-444130fd2751","printable":true,"keyId":"e1144e0a-3459-4109-8e9b-feaabb85bc3a","key":"Pustules all over body"},{"expression":"$Skin = 'BOIL'","name":"Big Boil","type":"sign","weight":"1.0","position":6,"symptomId":"929ca60e-61ec-47bb-8726-c52f14ecfab3","printable":true,"keyId":"d9226b55-5b85-4363-bb16-52a31c21a1c3","key":"Big Boil"},{"expression":"$Umbilicus = 'Inf'","name":"Infected umbilicus","type":"sign","weight":"1.0","position":7,"symptomId":"682966dd-4c19-4ab1-aa15-7b1921f01310","printable":true,"keyId":"568e168d-3fd4-4ad5-ad4b-f774bbc4569f","key":"Infected umbilicus"},{"expression":"$Fontanelle = 'Bulg'","name":"Bulging fontanelle","type":"sign","weight":"1.0","position":8,"symptomId":"68323f23-4a79-42ad-9909-fefc64460460","printable":true,"keyId":"b8a94b51-4469-4cd1-bf39-42205fcc005d","key":"Bulging fontanelle"},{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":9,"symptomId":"298989ba-06ad-45ad-ad3f-b58470df5913","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183","key":"Grunting or severe recessions"},{"expression":"$RespSR = 'Apn'","name":"Apneoa","type":"sign","weight":"1.0","position":10,"symptomId":"45c626fe-0083-4f8e-b57d-9e9126c1e740","printable":true,"keyId":"22f4f401-0541-4994-ad5c-22f2a9a659e1","key":"Apneoa"},{"expression":"$WOBSev = 'Sev'","name":"Severe WOB","type":"sign","weight":"1.0","position":11,"symptomId":"13a1854e-15a9-4a81-aca5-e6ca839c938b","printable":true,"keyId":"28ba5996-b2f2-4709-97f7-07246e2df9f4","key":"Severe WOB"},{"expression":"$WOBSev = 'Mod'","name":"Moderate WOB","type":"sign","weight":"1.0","position":12,"symptomId":"7af212a6-903a-4317-bbc3-150616980ff0","printable":true,"keyId":"d63ec530-2e03-41f0-82ca-9d078732734b","key":"Moderate WOB"},{"expression":"$AdmReason = 'Fev'","name":"Reason for admission - Fever","type":"sign","weight":"1.0","position":13,"symptomId":"8c74d86d-fe80-4734-a8a5-86ba59059804","printable":true,"keyId":"c6df56b0-2574-48c9-9866-ce02831969dd","key":"Reason for admission - Fever"},{"expression":"$SRNeuroOther = 'F'","name":"Other symptoms - Fever","type":"sign","weight":"1.0","position":14,"symptomId":"fea993f2-d228-4f00-8425-827fd5f99a9c","printable":true,"keyId":"029e7ca2-2aa9-4600-9aee-b22a5aecf0da","key":"Other symptoms - Fever"},{"expression":"$RR &gt; 59 and ($AgeCat = 'NB24' or $AgeCat = 'NB48' or $AgeCat = 'INF72')","name":"Tachypnoea &gt; 59 in all ages except &lt; 2hrs old","type":"sign","weight":"1.0","position":15,"symptomId":"8b47901b-cabf-4a02-8891-5f92856fbd59","printable":true,"keyId":"14ba42cb-bc23-4d31-ae51-3f4a756c4701","key":"Tachypnoea &gt; 59 in all ages except &lt; 2hrs old"},{"expression":"$Activity = 'Leth'","name":"Lethargic","type":"sign","weight":"1.0","position":16,"symptomId":"9289a7e1-1f30-42e5-88ff-4dced3fb7645","printable":true,"keyId":"5068af13-76b7-4a76-988d-4dabc945f304","key":"Lethargic"},{"expression":"$WOBSev = 'Mild'","name":"Mild WOB","type":"sign","weight":"0.5","position":17,"symptomId":"40c85580-e33b-428e-b7a7-767f308c0b5f","printable":true,"keyId":"31fef7a4-01fb-411e-8200-ed20bec16a3a","key":"Mild WOB"},{"expression":"($HR &gt; 159 and $Temperature &lt; 37.5) or ($HR &gt; 159 and $BabyCryTriage = true)","name":"Tachycardia without fever or crying","type":"sign","weight":"0.5","position":18,"symptomId":"5601f609-3b5a-497c-9674-4fb27b167abb","printable":true,"keyId":"0c50f955-57f7-48cb-9455-22ea5f23c72e","key":"Tachycardia without fever or crying"},{"expression":"$HRManual &gt; 159 and $Temperature &lt; 37.5","name":"Manual tachy without fever","type":"sign","weight":"0.5","position":19,"symptomId":"f5ad7207-caf6-4a4d-9cdb-d014ca73a123","printable":true,"keyId":"e5203db6-0bf6-45fe-bf0e-dae78ffc0871","key":"Manual tachy without fever"},{"expression":"$Colour = 'White'","name":"Pallor","type":"sign","weight":"0.5","position":20,"symptomId":"ca4679d6-906d-4c3d-b242-afd835a752ba","printable":true,"keyId":"b00e7d87-6725-4bbf-9fd1-712e35fb7f30","key":"Pallor"},{"expression":"$FeedingReview = 'NG' or $FeedingReview = 'IVF' or $Vomiting = 'Yes' or $Vomiting = 'YesBl'","name":"Poor feeding","type":"sign","weight":"0.5","position":21,"symptomId":"9d4f2151-3747-4b98-8023-5a5c1802f076","printable":true,"keyId":"94c3d0f7-71af-4069-bf59-2db364eedf7f","key":"Poor feeding"},{"expression":"($SuckReflex = 'Weak' or $SuckReflex = 'Absent') and $Gestation &gt; 33","name":"Weak Suck &amp; Gestation &gt; 33 weeks","type":"sign","weight":"0.5","position":22,"symptomId":"069b331a-12f2-4986-9e1e-4a147199c043","printable":true,"keyId":"97c07758-0787-4b02-9f3a-5a7a7d6f55b6","key":"Weak Suck &amp; Gestation &gt; 33 weeks"},{"expression":"$Activity = 'Irrit'","name":"Irritable","type":"sign","weight":"0.5","position":23,"symptomId":"5aeb3513-6fb6-408c-ba9c-cb68fb97f851","printable":true,"keyId":"55d2ba10-8cad-4618-a57b-211a2f5e64f4","key":"Irritable"},{"expression":"$RFSepsis = 'Pr2nd'","name":"Prolonged 2nd stage","type":"risk","weight":"1.0","position":24,"symptomId":"ff76a8e3-0e99-4758-b1d0-b1c263b931e1","printable":true,"keyId":"3c53da79-b51b-4c07-a0ee-d90172eadc5c","key":"Prolonged 2nd stage"},{"expression":"$RFSepsis = 'BBA'","name":"Born before arrival","type":"risk","weight":"0.5","position":25,"symptomId":"43abc519-92e8-41fe-b3e5-1d1e22a836d9","printable":true,"keyId":"34f53d47-f48f-4f33-a23e-dba8ae101ca1","key":"Born before arrival"},{"expression":"$Gestation &lt; 37 and $Gestation &gt; 31","name":"Prematurity 32-36","type":"risk","weight":"0.5","position":26,"symptomId":"46079fb8-5694-4845-92e5-c5a5ae4a13c0","printable":true,"keyId":"ed62f9ba-9c40-4a28-a209-e240685fe4ee","key":"Prematurity 32-36"},{"expression":"$Colour = 'Yell' and ($AgeCat = 'FNB' or $AgeCat = 'NB24')","name":"Jaundice &lt; 24 hrs","type":"sign","weight":"1.0","position":27,"symptomId":"d09d7a08-5d38-4af3-a558-34f1bcf48a70","printable":true,"keyId":"c6d9c843-e1fc-4422-9ee0-d76bdc94ecd2","key":"Jaundice &lt; 24 hrs"},{"expression":"$Gestation &lt; 32","name":"Very or extremely prem (&lt;32 wks)","type":"risk","weight":"1.0","position":28,"symptomId":"727357db-45f2-4042-ac54-76f1d9beb2c8","printable":true,"keyId":"6c849406-ad8c-4178-a278-0184363bf209","key":"Very or extremely prem (&lt;32 wks)"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":29,"symptomId":"27b1146c-00be-4aac-a1aa-afb03d24c877","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22","key":"Convulsions"},{"expression":"$Abdomen = 'Dist'","name":"Distended abdomen","type":"sign","weight":"0.5","position":30,"symptomId":"1478f323-98f4-4844-84a0-593d2dc8349b","printable":true,"keyId":"3b8cb379-ec7b-49b1-833c-8bbb8e525125","key":"Distended abdomen"},{"expression":"$Vomiting = 'YesGr'","name":"Bilious vomiting","type":"sign","weight":"1.0","position":31,"symptomId":"bc295b44-ed10-4b68-8890-7e1a9be72d67","printable":true,"keyId":"321ed112-b2f1-4c96-a74e-e5e4217b5bd5","key":"Bilious vomiting"},{"expression":"$RR &gt; 80 and $AgeCat = 'FNB'","name":"RR &gt; 80 in &lt; 2 hrs","type":"sign","weight":"1.0","position":32,"symptomId":"1c54d12f-bffd-4c18-b552-ec8f33201679","printable":true,"keyId":"6a4da821-d01d-4659-88d4-c59663b0bd6e","key":"RR &gt; 80 in &lt; 2 hrs"},{"expression":"$RR &gt; 59 and $RR &lt; 81 and $AgeCat = 'FNB'","name":"RR 60-80 &lt; 2hrs","type":"sign","weight":"0.5","position":33,"symptomId":"421565c9-6e19-42de-82ca-8f910ce4cd57","printable":true,"keyId":"871f773e-c361-4421-b95b-aefbce4b3ade","key":"RR 60-80 &lt; 2hrs"}]</v>
       </c>
       <c r="N16" t="str">
         <v>Clinical instructions to be added here</v>
@@ -16846,7 +16846,7 @@
         <v>Birth Trauma</v>
       </c>
       <c r="H17" t="str">
-        <v>2531</v>
+        <v>2999</v>
       </c>
       <c r="I17" t="str">
         <v>editor</v>
@@ -16923,7 +16923,7 @@
         <v>Apnoea of prematurity</v>
       </c>
       <c r="H18" t="str">
-        <v>2532</v>
+        <v>3000</v>
       </c>
       <c r="I18" t="str">
         <v>editor</v>
@@ -16938,7 +16938,7 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>[{"expression":"$RespSR = 'Apn'","name":"History of Apnoea","type":"sign","weight":"1.0","position":1,"symptomId":"d8066b75-01cc-4fb4-a9b2-96fd6d3ad697","printable":true,"keyId":"9e18e7fc-f134-41af-aa5a-faf95d633c7f"},{"expression":"$RespSR = 'BE'","name":"History of blue episodes","type":"sign","weight":"1.0","position":2,"symptomId":"ba4f3d1c-04e5-48b1-af08-0094d2d0c555","printable":true,"keyId":"49013b45-d908-4119-868a-d6cd226fbeaf"}]</v>
+        <v>[{"expression":"$RespSR = 'Apn'","name":"History of Apnoea","type":"sign","weight":"1.0","position":1,"symptomId":"d8066b75-01cc-4fb4-a9b2-96fd6d3ad697","printable":true,"keyId":"9e18e7fc-f134-41af-aa5a-faf95d633c7f","key":"History of Apnoea"},{"expression":"$RespSR = 'BE'","name":"History of blue episodes","type":"sign","weight":"1.0","position":2,"symptomId":"ba4f3d1c-04e5-48b1-af08-0094d2d0c555","printable":true,"keyId":"49013b45-d908-4119-868a-d6cd226fbeaf","key":"History of blue episodes"}]</v>
       </c>
       <c r="N18" t="str">
         <v>Clinical instructions to be added here</v>
@@ -17000,7 +17000,7 @@
         <v>Birth Asphyxia</v>
       </c>
       <c r="H19" t="str">
-        <v>2533</v>
+        <v>3001</v>
       </c>
       <c r="I19" t="str">
         <v>editor</v>
@@ -17015,7 +17015,7 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>[{"expression":"$Reason = 'FD'","name":"Foetal distress","type":"risk","weight":"1.0","position":1,"symptomId":"a3f04a3a-d417-4783-a61a-ce06ec478b08","printable":true,"keyId":"3efb4dcc-ad4c-462f-b595-0a48deab71fa"},{"expression":"$RFSepsis = 'Pr2nd'","name":"Prolonged 2nd stage","type":"risk","weight":"1.0","position":2,"symptomId":"cf2c8eae-b49b-4a2e-ad87-832b02893141","printable":true,"keyId":"3c53da79-b51b-4c07-a0ee-d90172eadc5c"},{"expression":"$ModeDelivery = '2' or $ModeDelivery = '5' or $ModeDelivery = '6'","name":"Mode of delivery Vacuum/EmCS/Breech vaginal","type":"risk","weight":"1.0","position":3,"symptomId":"b4a92c2d-fcab-41c8-8b98-35cf8f815583","printable":true,"keyId":"46fd13f0-91c1-4fe8-9a9b-cbd3d8341882"},{"expression":"$Apgar5 &lt; 7","name":"Apgar at 5 min &lt; 7","type":"risk","weight":"1.0","position":4,"symptomId":"619fcb57-2186-4f49-abe6-d459fc2cf07c","printable":true,"keyId":"b265d8ec-2724-4b3d-bdf4-c22470fa6019"},{"expression":"($Resus = 'BVM' and $LengthResus &gt; 5) or $Resus = 'CPR' or $LengthResus &gt; 10 ","name":"Resus: &gt; 10 mins or (BVM &gt; 5 mins) or any CPR ","type":"risk","weight":"1.0","position":5,"symptomId":"f47a5125-5dee-4174-abf9-4bc580eb79fe","printable":true,"keyId":"4e36f8b1-e511-4bd2-b1a8-d9a18df05563"},{"expression":"$SuckReflex = 'Absent' and $Gestation &gt; 33","name":"Absent suck reflex &amp; Gestation 34 weeks or more","type":"sign","weight":"1.0","position":6,"symptomId":"52af9b4a-192d-4cf4-8e86-a4468aeaee84","printable":true,"keyId":"8e33a3f2-a4b9-4636-89c1-ace2a65f6838"},{"expression":"$Tone = 'Low'","name":"Hypotonia","type":"sign","weight":"1.0","position":7,"symptomId":"dc2ae889-a6e8-4071-a87f-3fd4d105fe68","printable":true,"keyId":"f83f4a58-cf2f-4292-8e65-e72a55dd9f98"},{"expression":"$Activity = 'Irrit' or $Activity = 'Leth' or $Activity = 'Coma'","name":"Activity irritable or lethargic or Coma","type":"sign","weight":"1.0","position":8,"symptomId":"62ab5739-7456-4cf8-b9bf-525f14614343","printable":true,"keyId":"03d33783-accc-4eca-ac53-536698a70822"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":9,"symptomId":"6bc3a987-bf77-4ca3-958e-16c493aa3782","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22"},{"expression":"$MSKproblems = 'BTUL' or $MSKproblems = 'BTLL' or $HeadShape = 'Swell'","name":"Birth Trauma","type":"risk","weight":"1.0","position":10,"symptomId":"f92feba0-78aa-4b09-85a6-b72a9297db32","printable":true,"keyId":"92c138b6-6762-4efc-bfca-d5b0e8c5b367"}]</v>
+        <v>[{"expression":"$Reason = 'FD'","name":"Foetal distress","type":"risk","weight":"1.0","position":1,"symptomId":"a3f04a3a-d417-4783-a61a-ce06ec478b08","printable":true,"keyId":"3efb4dcc-ad4c-462f-b595-0a48deab71fa","key":"Foetal distress"},{"expression":"$RFSepsis = 'Pr2nd'","name":"Prolonged 2nd stage","type":"risk","weight":"1.0","position":2,"symptomId":"cf2c8eae-b49b-4a2e-ad87-832b02893141","printable":true,"keyId":"3c53da79-b51b-4c07-a0ee-d90172eadc5c","key":"Prolonged 2nd stage"},{"expression":"$ModeDelivery = '2' or $ModeDelivery = '5' or $ModeDelivery = '6'","name":"Mode of delivery Vacuum/EmCS/Breech vaginal","type":"risk","weight":"1.0","position":3,"symptomId":"b4a92c2d-fcab-41c8-8b98-35cf8f815583","printable":true,"keyId":"46fd13f0-91c1-4fe8-9a9b-cbd3d8341882","key":"Mode of delivery Vacuum/EmCS/Breech vaginal"},{"expression":"$Apgar5 &lt; 7","name":"Apgar at 5 min &lt; 7","type":"risk","weight":"1.0","position":4,"symptomId":"619fcb57-2186-4f49-abe6-d459fc2cf07c","printable":true,"keyId":"b265d8ec-2724-4b3d-bdf4-c22470fa6019","key":"Apgar at 5 min &lt; 7"},{"expression":"($Resus = 'BVM' and $LengthResus &gt; 5) or $Resus = 'CPR' or $LengthResus &gt; 10 ","name":"Resus: &gt; 10 mins or (BVM &gt; 5 mins) or any CPR","type":"risk","weight":"1.0","position":5,"symptomId":"f47a5125-5dee-4174-abf9-4bc580eb79fe","printable":true,"keyId":"4e36f8b1-e511-4bd2-b1a8-d9a18df05563","key":"Resus: &gt; 10 mins or (BVM &gt; 5 mins) or any CPR"},{"expression":"$SuckReflex = 'Absent' and $Gestation &gt; 33","name":"Absent suck reflex &amp; Gestation 34 weeks or more","type":"sign","weight":"1.0","position":6,"symptomId":"52af9b4a-192d-4cf4-8e86-a4468aeaee84","printable":true,"keyId":"8e33a3f2-a4b9-4636-89c1-ace2a65f6838","key":"Absent suck reflex &amp; Gestation 34 weeks or more"},{"expression":"$Tone = 'Low'","name":"Hypotonia","type":"sign","weight":"1.0","position":7,"symptomId":"dc2ae889-a6e8-4071-a87f-3fd4d105fe68","printable":true,"keyId":"f83f4a58-cf2f-4292-8e65-e72a55dd9f98","key":"Hypotonia"},{"expression":"$Activity = 'Irrit' or $Activity = 'Leth' or $Activity = 'Coma'","name":"Activity irritable or lethargic or Coma","type":"sign","weight":"1.0","position":8,"symptomId":"62ab5739-7456-4cf8-b9bf-525f14614343","printable":true,"keyId":"03d33783-accc-4eca-ac53-536698a70822","key":"Activity irritable or lethargic or Coma"},{"expression":"$DangerSigns = 'Conv' or $SRNeuroOther = 'Conv' or $Activity = 'Conv'","name":"Convulsions","type":"sign","weight":"1.0","position":9,"symptomId":"6bc3a987-bf77-4ca3-958e-16c493aa3782","printable":true,"keyId":"5e197b89-cbae-4b9e-b7cd-c41f64994f22","key":"Convulsions"},{"expression":"$MSKproblems = 'BTUL' or $MSKproblems = 'BTLL' or $HeadShape = 'Swell'","name":"Birth Trauma","type":"risk","weight":"1.0","position":10,"symptomId":"f92feba0-78aa-4b09-85a6-b72a9297db32","printable":true,"keyId":"92c138b6-6762-4efc-bfca-d5b0e8c5b367","key":"Birth Trauma"}]</v>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -17077,7 +17077,7 @@
         <v>Convulsions</v>
       </c>
       <c r="H20" t="str">
-        <v>2534</v>
+        <v>3002</v>
       </c>
       <c r="I20" t="str">
         <v>editor</v>
@@ -17092,7 +17092,7 @@
         <v>Convulsions seen on examination or history</v>
       </c>
       <c r="M20" t="str">
-        <v>[{"expression":"$DangerSigns = 'Conv'","name":"Convulsions in Danger Signs","type":"sign","weight":"1.0","position":1,"symptomId":"db5122a5-6f8d-4f7a-bed6-efd20de4c95f","printable":true,"keyId":"e87925bc-e337-40e5-aed9-7c834adbc702"},{"expression":"$SRNeuroOther = 'Conv'","name":"History of convulsions","type":"sign","weight":"1.0","position":2,"symptomId":"7bb311b5-e2c5-4a99-8e85-8cafe79631ca","printable":true,"keyId":"7eb23a0c-be93-420a-bc51-15ac3ea82e76"},{"expression":"$Activity = 'Conv'","name":"Activity is convulsing","type":"sign","weight":"1.0","position":3,"symptomId":"21236f05-f0d6-4a09-8a70-a4a23782b9ac","printable":true,"keyId":"ddbc818e-f0ce-47a3-9b00-cb2a3132d44d"},{"expression":"$AdmReason = 'Conv'","name":"Presented with convulsions","type":"sign","weight":"1.0","position":4,"symptomId":"8b93398e-44ee-4834-8d9b-d93513e37f3e","printable":true,"keyId":"3673c224-36e2-4bcb-acca-9ce58ab2ad3f"}]</v>
+        <v>[{"expression":"$DangerSigns = 'Conv'","name":"Convulsions in Danger Signs","type":"sign","weight":"1.0","position":1,"symptomId":"db5122a5-6f8d-4f7a-bed6-efd20de4c95f","printable":true,"keyId":"e87925bc-e337-40e5-aed9-7c834adbc702","key":"Convulsions in Danger Signs"},{"expression":"$SRNeuroOther = 'Conv'","name":"History of convulsions","type":"sign","weight":"1.0","position":2,"symptomId":"7bb311b5-e2c5-4a99-8e85-8cafe79631ca","printable":true,"keyId":"7eb23a0c-be93-420a-bc51-15ac3ea82e76","key":"History of convulsions"},{"expression":"$Activity = 'Conv'","name":"Activity is convulsing","type":"sign","weight":"1.0","position":3,"symptomId":"21236f05-f0d6-4a09-8a70-a4a23782b9ac","printable":true,"keyId":"ddbc818e-f0ce-47a3-9b00-cb2a3132d44d","key":"Activity is convulsing"},{"expression":"$AdmReason = 'Conv'","name":"Presented with convulsions","type":"sign","weight":"1.0","position":4,"symptomId":"8b93398e-44ee-4834-8d9b-d93513e37f3e","printable":true,"keyId":"3673c224-36e2-4bcb-acca-9ce58ab2ad3f","key":"Presented with convulsions"}]</v>
       </c>
       <c r="N20" t="str" xml:space="preserve">
         <v xml:space="preserve">Refer to management of convulsions flow chart on wall
@@ -17168,7 +17168,7 @@
         <v>Low Birth Weight (1500-2499g)</v>
       </c>
       <c r="H21" t="str">
-        <v>2535</v>
+        <v>3003</v>
       </c>
       <c r="I21" t="str">
         <v>editor</v>
@@ -17253,7 +17253,7 @@
         <v>Very Low Birth Weight (1000-1499g)</v>
       </c>
       <c r="H22" t="str">
-        <v>2536</v>
+        <v>3004</v>
       </c>
       <c r="I22" t="str">
         <v>editor</v>
@@ -17339,7 +17339,7 @@
         <v>Extremely Low Birth Weight (&lt;1000g)</v>
       </c>
       <c r="H23" t="str">
-        <v>2537</v>
+        <v>3005</v>
       </c>
       <c r="I23" t="str">
         <v>editor</v>
@@ -17425,7 +17425,7 @@
         <v>High Birth Weight (&gt;4000g at birth)</v>
       </c>
       <c r="H24" t="str">
-        <v>2538</v>
+        <v>3006</v>
       </c>
       <c r="I24" t="str">
         <v>editor</v>
@@ -17502,7 +17502,7 @@
         <v>Mild Hypothermia</v>
       </c>
       <c r="H25" t="str">
-        <v>2539</v>
+        <v>3007</v>
       </c>
       <c r="I25" t="str">
         <v>editor</v>
@@ -17587,7 +17587,7 @@
         <v>Moderate Hypothermia</v>
       </c>
       <c r="H26" t="str">
-        <v>2540</v>
+        <v>3008</v>
       </c>
       <c r="I26" t="str">
         <v>editor</v>
@@ -17672,7 +17672,7 @@
         <v>Severe Hypothermia</v>
       </c>
       <c r="H27" t="str">
-        <v>2541</v>
+        <v>3009</v>
       </c>
       <c r="I27" t="str">
         <v>editor</v>
@@ -17757,7 +17757,7 @@
         <v>Hyperthermia</v>
       </c>
       <c r="H28" t="str">
-        <v>2542</v>
+        <v>3010</v>
       </c>
       <c r="I28" t="str">
         <v>editor</v>
@@ -17835,7 +17835,7 @@
         <v>Premature (32-36 weeks)</v>
       </c>
       <c r="H29" t="str">
-        <v>2543</v>
+        <v>3011</v>
       </c>
       <c r="I29" t="str">
         <v>editor</v>
@@ -17929,7 +17929,7 @@
         <v>Very Premature (28-31 weeks)</v>
       </c>
       <c r="H30" t="str">
-        <v>2544</v>
+        <v>3012</v>
       </c>
       <c r="I30" t="str">
         <v>editor</v>
@@ -18023,7 +18023,7 @@
         <v>Extremely Premature (&lt;28 weeks)</v>
       </c>
       <c r="H31" t="str">
-        <v>2545</v>
+        <v>3013</v>
       </c>
       <c r="I31" t="str">
         <v>editor</v>
@@ -18117,7 +18117,7 @@
         <v>Hypoglycaemia (symptomatic)</v>
       </c>
       <c r="H32" t="str">
-        <v>2546</v>
+        <v>3014</v>
       </c>
       <c r="I32" t="str">
         <v>editor</v>
@@ -18199,7 +18199,7 @@
         <v>Hypoglycaemia (NOT symptomatic)</v>
       </c>
       <c r="H33" t="str">
-        <v>2547</v>
+        <v>3015</v>
       </c>
       <c r="I33" t="str">
         <v>editor</v>
@@ -18278,7 +18278,7 @@
         <v>At Risk of Hypoglycaemia</v>
       </c>
       <c r="H34" t="str">
-        <v>2548</v>
+        <v>3016</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -18370,7 +18370,7 @@
         <v>HIV Unknown</v>
       </c>
       <c r="H35" t="str">
-        <v>2549</v>
+        <v>3017</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -18459,7 +18459,7 @@
         <v>HIV Low Risk</v>
       </c>
       <c r="H36" t="str">
-        <v>2550</v>
+        <v>3018</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -18542,7 +18542,7 @@
         <v>HIV High Risk</v>
       </c>
       <c r="H37" t="str">
-        <v>2551</v>
+        <v>3019</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -18630,7 +18630,7 @@
         <v>Physiological Jaundice</v>
       </c>
       <c r="H38" t="str">
-        <v>2552</v>
+        <v>3020</v>
       </c>
       <c r="I38" t="str">
         <v>editor</v>
@@ -18659,7 +18659,7 @@
         <v xml:space="preserve">3. Educate parents on how to monitor for jaundice </v>
       </c>
       <c r="Q38" t="str">
-        <v>{"data":"https://webeditor.neotree.org/files/361b5b75-8599-415a-b25d-f4586c3dbe8c?height=446&amp;width=642","fileId":"361b5b75-8599-415a-b25d-f4586c3dbe8c","filename":"Jaundice.png","size":"127149"}</v>
+        <v>{"data":"https://webeditor.neotree.org/files/361b5b75-8599-415a-b25d-f4586c3dbe8c?height=446&amp;type=png&amp;width=642","fileId":"361b5b75-8599-415a-b25d-f4586c3dbe8c","filename":"Jaundice.png","size":"127149"}</v>
       </c>
       <c r="R38" t="str">
         <v>{"data":"https://webeditor.neotree.org/files/9c741b43-cea6-4b95-824b-3f5dc657f0d1?height=550&amp;width=790","fileId":"9c741b43-cea6-4b95-824b-3f5dc657f0d1","filename":"COIN_Jaund2.png","size":"86572"}</v>
@@ -18709,7 +18709,7 @@
         <v>Pathological Jaundice</v>
       </c>
       <c r="H39" t="str">
-        <v>2553</v>
+        <v>3021</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -18800,7 +18800,7 @@
         <v>Prolonged Jaundice</v>
       </c>
       <c r="H40" t="str">
-        <v>2554</v>
+        <v>3022</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -18881,7 +18881,7 @@
         <v>Hypoxic Ischaemic Encephalopathy</v>
       </c>
       <c r="H41" t="str">
-        <v>2555</v>
+        <v>3023</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -18972,7 +18972,7 @@
         <v>Suspected Hypoxic Ischaemic Encephalopathy</v>
       </c>
       <c r="H42" t="str">
-        <v>2556</v>
+        <v>3024</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -19063,7 +19063,7 @@
         <v>Prematurity with Respiratory Distress</v>
       </c>
       <c r="H43" t="str">
-        <v>2557</v>
+        <v>3025</v>
       </c>
       <c r="I43" t="str">
         <v>editor</v>
@@ -19078,7 +19078,7 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"54e4b47a-5083-409b-b9ae-fb69ef31f5db","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183"},{"expression":"$RR &gt; 80","name":"Tachypnoea &gt; 80","type":"sign","weight":"1.0","position":2,"symptomId":"cfa391fc-d88f-4f36-8b01-47b3dcf009f9","printable":true,"keyId":"12de2633-b99b-448d-97f8-dadd21f5b8a8"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":3,"symptomId":"eec8c7a4-6e77-4d04-8c46-41425e5766ab","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":4,"symptomId":"9f5cfd09-beb8-418a-af7b-545abc697d12","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of WOB","type":"sign","weight":"1.0","position":5,"symptomId":"852421c4-4b0b-443e-acd3-25a7fca7550d","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb"},{"expression":"$SatsAIr &lt; 90","name":"Saturations in air &lt; 90","type":"sign","weight":"1.0","position":6,"symptomId":"475f2c37-a801-4921-bebd-ac0b14422dc9","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in oxygen &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"3664170c-70e9-4b69-b151-e5e3026804eb","printable":true,"keyId":"ff5acafd-9c6f-4cee-b3b4-fd78ef191f91"}]</v>
+        <v>[{"expression":"$DangerSigns = 'Grun'","name":"Grunting or severe recessions","type":"sign","weight":"1.0","position":1,"symptomId":"54e4b47a-5083-409b-b9ae-fb69ef31f5db","printable":true,"keyId":"ff679937-e2ae-4783-a102-b5968e9aa183","key":"Grunting or severe recessions"},{"expression":"$RR &gt; 80","name":"Tachypnoea &gt; 80","type":"sign","weight":"1.0","position":2,"symptomId":"cfa391fc-d88f-4f36-8b01-47b3dcf009f9","printable":true,"keyId":"12de2633-b99b-448d-97f8-dadd21f5b8a8","key":"Tachypnoea &gt; 80"},{"expression":"$RespSR = 'DIB'","name":"History of fast or laboured breathing","type":"sign","weight":"1.0","position":3,"symptomId":"eec8c7a4-6e77-4d04-8c46-41425e5766ab","printable":true,"keyId":"d68e9dd5-78d8-4cac-bc49-eab88a22ff3f","key":"History of fast or laboured breathing"},{"expression":"$RespSR = 'NBr'","name":"History of noisy breathing","type":"sign","weight":"1.0","position":4,"symptomId":"9f5cfd09-beb8-418a-af7b-545abc697d12","printable":true,"keyId":"8fc575f5-b9c5-4c7a-9cd5-ce6d167d2904","key":"History of noisy breathing"},{"expression":"$WOBSev = 'Mild' or $WOBSev = 'Mod' or $WOBSev = 'Sev'","name":"Any severity of WOB","type":"sign","weight":"1.0","position":5,"symptomId":"852421c4-4b0b-443e-acd3-25a7fca7550d","printable":true,"keyId":"f77045fb-04bd-467c-ad6f-24bd707f10eb","key":"Any severity of WOB"},{"expression":"$SatsAIr &lt; 90","name":"Saturations in air &lt; 90","type":"sign","weight":"1.0","position":6,"symptomId":"475f2c37-a801-4921-bebd-ac0b14422dc9","printable":true,"keyId":"ae41036d-64ee-4d96-a91a-b205b8c54ec2","key":"Saturations in air &lt; 90"},{"expression":"$SatsO2 &lt; 90","name":"Saturations in oxygen &lt; 90","type":"sign","weight":"1.0","position":7,"symptomId":"3664170c-70e9-4b69-b151-e5e3026804eb","printable":true,"keyId":"ff5acafd-9c6f-4cee-b3b4-fd78ef191f91","key":"Saturations in oxygen &lt; 90"}]</v>
       </c>
       <c r="N43" t="str" xml:space="preserve">
         <v xml:space="preserve">Care must be given to thermoregulation as per preterm guidelines
@@ -19161,7 +19161,7 @@
         <v>Term baby with Respiratory Distress</v>
       </c>
       <c r="H44" t="str">
-        <v>2558</v>
+        <v>3026</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -19258,7 +19258,7 @@
         <v>Gastroschisis</v>
       </c>
       <c r="H45" t="str">
-        <v>2559</v>
+        <v>3027</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -19345,7 +19345,7 @@
         <v>Omphalocele</v>
       </c>
       <c r="H46" t="str">
-        <v>2560</v>
+        <v>3028</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -19430,7 +19430,7 @@
         <v>Cleft lip and/or palate with RD</v>
       </c>
       <c r="H47" t="str">
-        <v>2561</v>
+        <v>3029</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -19512,7 +19512,7 @@
         <v>Cleft lip</v>
       </c>
       <c r="H48" t="str">
-        <v>2562</v>
+        <v>3030</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -19594,7 +19594,7 @@
         <v>Cleft lip and/or palate</v>
       </c>
       <c r="H49" t="str">
-        <v>2563</v>
+        <v>3031</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -19680,7 +19680,7 @@
         <v>Myelomeningocele</v>
       </c>
       <c r="H50" t="str">
-        <v>2564</v>
+        <v>3032</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -19764,7 +19764,7 @@
         <v>Congenital dislocation of the hip (CDH)</v>
       </c>
       <c r="H51" t="str">
-        <v>2565</v>
+        <v>3033</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -19846,7 +19846,7 @@
         <v>Moderate Talipes (club foot)</v>
       </c>
       <c r="H52" t="str">
-        <v>2566</v>
+        <v>3034</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -19925,7 +19925,7 @@
         <v>Mild Talipes (club foot)</v>
       </c>
       <c r="H53" t="str">
-        <v>2567</v>
+        <v>3035</v>
       </c>
       <c r="I53" t="str">
         <v/>
